--- a/Calculation.xlsx
+++ b/Calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c0d169820723523/Uni/Aerospace Master/1. Semester/Aerospace Strcutures/Assignment 2/AerospaceStructures_Assignment2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{4071ACE8-B8E8-7F45-AA5C-44E61B53CA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B94EAC12-60B2-4292-B33A-31B5946E43C2}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{4071ACE8-B8E8-7F45-AA5C-44E61B53CA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471096F5-3BA6-4B3C-AAD3-2B1CF6E55BE5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{774086B3-7ADF-614D-BABB-EF0864783B0B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="8" xr2:uid="{774086B3-7ADF-614D-BABB-EF0864783B0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Import_UngaBunga" sheetId="11" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Results_final" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -702,20 +703,20 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Gut" xfId="2" builtinId="26"/>
@@ -724,7 +725,7 @@
     <cellStyle name="Schlecht" xfId="3" builtinId="27"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -747,31 +748,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1739,6 +1720,10 @@
 </inkml:ink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -3164,8 +3149,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <f>MIN(Import_UngaBunga!B2,Import_UngaBunga!F2)</f>
-        <v>-66.018310546875</v>
+        <v>-20</v>
       </c>
       <c r="C2">
         <f>MIN(Import_UngaBunga!C2,Import_UngaBunga!G2)</f>
@@ -4413,7 +4397,7 @@
       </c>
       <c r="C2">
         <f>SQRT(Import!B2^2+Import!F2^2-Import!B2*Import!F2+3*Import!D2^2)</f>
-        <v>101.05026725087633</v>
+        <v>72.124359998856804</v>
       </c>
       <c r="D2">
         <f>SQRT(Import!C2^2+Import!G2^2-Import!C2*Import!G2+3*Import!E2^2)</f>
@@ -4429,7 +4413,7 @@
       </c>
       <c r="H2" s="8">
         <f>IF(C2&lt;&gt;0,$A$2/(1.5*C2),IF(E2&lt;&gt;0,$A$2/(1.5*E2),"NaN"))</f>
-        <v>3.5083529182544098</v>
+        <v>4.915398902751015</v>
       </c>
       <c r="I2" s="8">
         <f>IF(D2&lt;&gt;0,$A$2/(1.5*D2),IF(F2&lt;&gt;0,$A$2/(1.5*F2),"NaN"))</f>
@@ -6311,14 +6295,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="D1" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="D1" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="20"/>
+      <c r="E1" s="21"/>
       <c r="G1" t="s">
         <v>87</v>
       </c>
@@ -6329,7 +6313,7 @@
         <v>62</v>
       </c>
       <c r="L1" s="22"/>
-      <c r="M1" s="23"/>
+      <c r="M1" s="19"/>
       <c r="N1" s="22" t="s">
         <v>64</v>
       </c>
@@ -6354,17 +6338,17 @@
       <c r="H2">
         <v>600</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="23">
+      <c r="L2" s="19">
         <v>4</v>
       </c>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23" t="s">
+      <c r="M2" s="19"/>
+      <c r="N2" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="O2" s="23">
+      <c r="O2" s="19">
         <v>5</v>
       </c>
     </row>
@@ -6387,17 +6371,17 @@
       <c r="H3">
         <v>200</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="19">
         <v>65</v>
       </c>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="19">
         <v>28</v>
       </c>
     </row>
@@ -6414,17 +6398,17 @@
       <c r="E4">
         <v>2.4</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="19">
         <v>42</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23" t="s">
+      <c r="M4" s="19"/>
+      <c r="N4" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="19">
         <v>2.4</v>
       </c>
     </row>
@@ -6441,17 +6425,17 @@
       <c r="E5">
         <v>20</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="19">
         <v>3</v>
       </c>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23" t="s">
+      <c r="M5" s="19"/>
+      <c r="N5" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="19">
         <v>20</v>
       </c>
     </row>
@@ -6460,7 +6444,7 @@
         <v>68</v>
       </c>
       <c r="B6">
-        <v>2.1</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>68</v>
@@ -6468,17 +6452,17 @@
       <c r="E6" s="11">
         <v>15</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="19">
         <v>2.1</v>
       </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23" t="s">
+      <c r="M6" s="19"/>
+      <c r="N6" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="20">
         <v>15</v>
       </c>
     </row>
@@ -6497,7 +6481,7 @@
       </c>
       <c r="B34">
         <f>B3*B5 + (B4-B5)*B6</f>
-        <v>276.89999999999998</v>
+        <v>975</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6506,7 +6490,7 @@
       </c>
       <c r="B35">
         <f>B34*H2</f>
-        <v>166140</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6541,7 +6525,7 @@
       </c>
       <c r="B42" s="17">
         <f>B40*(10*B32+B35*4 + B38*5) * 10^3</f>
-        <v>16.397640000000003</v>
+        <v>20.921328000000003</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6561,11 +6545,11 @@
     <mergeCell ref="N1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B42">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>19.585</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>19585</formula>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+      <formula>19.585</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6643,34 +6627,34 @@
       <c r="B2">
         <v>156002.72424842999</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="23">
         <v>1</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="23">
         <f>SUM(B2:B4)</f>
         <v>468000.27897996001</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B2:$B4,Import!B2:B4)/$D2</f>
-        <v>-70.752968545441874</v>
-      </c>
-      <c r="F2" s="21">
+        <v>-55.413272966050641</v>
+      </c>
+      <c r="F2" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B2:$B4,Import!C2:C4)/$D2</f>
         <v>-23.279955056006532</v>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B2:$B4,Import!D2:D4)/$D2</f>
         <v>39.399464897236562</v>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B2:$B4,Import!E2:E4)/$D2</f>
         <v>155.56517208700083</v>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B2:$B4,Import!F2:F4)/$D2</f>
         <v>23.846147653298427</v>
       </c>
-      <c r="J2" s="21">
+      <c r="J2" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B2:$B4,Import!G2:G4)/$D2</f>
         <v>7.8462151433468197</v>
       </c>
@@ -6683,7 +6667,7 @@
       </c>
       <c r="M2" cm="1">
         <f t="array" ref="M2:M11">_xlfn._xlws.FILTER(E2:E31,E2:E31&lt;&gt;"")</f>
-        <v>-70.752968545441874</v>
+        <v>-55.413272966050641</v>
       </c>
       <c r="N2" cm="1">
         <f t="array" ref="N2:N11">_xlfn._xlws.FILTER(F2:F31,F2:F31&lt;&gt;"")</f>
@@ -6698,14 +6682,14 @@
       <c r="B3">
         <v>156000.05690826001</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
       <c r="K3">
         <v>2</v>
       </c>
@@ -6727,14 +6711,14 @@
       <c r="B4">
         <v>155997.49782327001</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
       <c r="K4">
         <v>3</v>
       </c>
@@ -6756,34 +6740,34 @@
       <c r="B5">
         <v>155997.49556549999</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="23">
         <v>2</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="23">
         <f t="shared" ref="D5" si="0">SUM(B5:B7)</f>
         <v>468000.27741465002</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B5:$B7,Import!B5:B7)/$D5</f>
         <v>-91.457956292773275</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B5:$B7,Import!C5:C7)/$D5</f>
         <v>-30.092478229483675</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B5:$B7,Import!D5:D7)/$D5</f>
         <v>39.032756873157155</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B5:$B7,Import!E5:E7)/$D5</f>
         <v>154.11746042478134</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B5:$B7,Import!F5:F7)/$D5</f>
         <v>23.846152654191794</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B5:$B7,Import!G5:G7)/$D5</f>
         <v>7.8462545426913328</v>
       </c>
@@ -6808,14 +6792,14 @@
       <c r="B6">
         <v>156000.05517224999</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
       <c r="K6">
         <v>5</v>
       </c>
@@ -6837,14 +6821,14 @@
       <c r="B7">
         <v>156002.7266769</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
       <c r="K7">
         <v>6</v>
       </c>
@@ -6866,34 +6850,34 @@
       <c r="B8">
         <v>155999.82694182999</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="23">
         <v>3</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="23">
         <f t="shared" ref="D8" si="1">SUM(B8:B10)</f>
         <v>467995.54139105999</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B8:$B10,Import!B8:B10)/$D8</f>
         <v>-93.462360205020303</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B8:$B10,Import!C8:C10)/$D8</f>
         <v>-30.752011325182355</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B8:$B10,Import!D8:D10)/$D8</f>
         <v>39.135793297071388</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B8:$B10,Import!E8:E10)/$D8</f>
         <v>154.52201225594342</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B8:$B10,Import!F8:F10)/$D8</f>
         <v>23.846018873279803</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B8:$B10,Import!G8:G10)/$D8</f>
         <v>7.8456136776305456</v>
       </c>
@@ -6918,14 +6902,14 @@
       <c r="B9">
         <v>155997.49996402999</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
       <c r="K9">
         <v>8</v>
       </c>
@@ -6947,14 +6931,14 @@
       <c r="B10">
         <v>155998.21448520001</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
       <c r="K10">
         <v>9</v>
       </c>
@@ -6976,34 +6960,34 @@
       <c r="B11">
         <v>155999.85662827999</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="23">
         <v>4</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="23">
         <f t="shared" ref="D11" si="2">SUM(B11:B13)</f>
         <v>468003.10705311992</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B11:$B13,Import!B11:B13)/$D11</f>
         <v>-93.222038415665409</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B11:$B13,Import!C11:C13)/$D11</f>
         <v>-30.673498199284161</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B11:$B13,Import!D11:D13)/$D11</f>
         <v>39.14346902990939</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B11:$B13,Import!E11:E13)/$D11</f>
         <v>154.55405316501287</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B11:$B13,Import!F11:F13)/$D11</f>
         <v>23.846320774572309</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B11:$B13,Import!G11:G13)/$D11</f>
         <v>7.8467995813713021</v>
       </c>
@@ -7028,14 +7012,14 @@
       <c r="B12">
         <v>156001.69767331</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
@@ -7045,14 +7029,14 @@
       <c r="B13">
         <v>156001.55275152999</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
       <c r="K13">
         <v>1</v>
       </c>
@@ -7077,34 +7061,34 @@
       <c r="B14">
         <v>156000.87944320001</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="23">
         <v>5</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="23">
         <f t="shared" ref="D14" si="3">SUM(B14:B16)</f>
         <v>468000.70313752</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B14:$B16,Import!B14:B16)/$D14</f>
         <v>-92.821111081150789</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B14:$B16,Import!C14:C16)/$D14</f>
         <v>-30.540989580149905</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B14:$B16,Import!D14:D16)/$D14</f>
         <v>39.142242190929672</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B14:$B16,Import!E14:E16)/$D14</f>
         <v>154.54799228379497</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B14:$B16,Import!F14:F16)/$D14</f>
         <v>23.846146263511852</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B14:$B16,Import!G14:G16)/$D14</f>
         <v>7.8461398628633692</v>
       </c>
@@ -7129,14 +7113,14 @@
       <c r="B15">
         <v>156000.16178102</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
       <c r="K15">
         <v>3</v>
       </c>
@@ -7158,14 +7142,14 @@
       <c r="B16">
         <v>155999.66191329999</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
       <c r="K16">
         <v>4</v>
       </c>
@@ -7187,34 +7171,34 @@
       <c r="B17">
         <v>155999.65820132001</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="23">
         <v>6</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="23">
         <f t="shared" ref="D17" si="4">SUM(B17:B19)</f>
         <v>467998.74598031002</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B17:$B19,Import!B17:B19)/$D17</f>
         <v>-92.705718918306388</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B17:$B19,Import!C17:C19)/$D17</f>
         <v>-30.503161720129956</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B17:$B19,Import!D17:D19)/$D17</f>
         <v>39.142009467321579</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B17:$B19,Import!E17:E19)/$D17</f>
         <v>154.54711478427072</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B17:$B19,Import!F17:F19)/$D17</f>
         <v>23.846132839911412</v>
       </c>
-      <c r="J17" s="21">
+      <c r="J17" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B17:$B19,Import!G17:G19)/$D17</f>
         <v>7.8460788562613226</v>
       </c>
@@ -7239,14 +7223,14 @@
       <c r="B18">
         <v>155999.66300462</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
       <c r="K18">
         <v>6</v>
       </c>
@@ -7268,14 +7252,14 @@
       <c r="B19">
         <v>155999.42477437001</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
       <c r="K19">
         <v>7</v>
       </c>
@@ -7297,34 +7281,34 @@
       <c r="B20">
         <v>156000.16264903001</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="23">
         <v>7</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="23">
         <f t="shared" ref="D20" si="5">SUM(B20:B22)</f>
         <v>468001.20399019995</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B20:$B22,Import!B20:B22)/$D20</f>
         <v>-93.424368299081564</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B20:$B22,Import!C20:C22)/$D20</f>
         <v>-30.739834806709119</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B20:$B22,Import!D20:D22)/$D20</f>
         <v>39.144665401201102</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B20:$B22,Import!E20:E22)/$D20</f>
         <v>154.55816907323165</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B20:$B22,Import!F20:F22)/$D20</f>
         <v>23.846126383365522</v>
       </c>
-      <c r="J20" s="21">
+      <c r="J20" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B20:$B22,Import!G20:G22)/$D20</f>
         <v>7.84604327052398</v>
       </c>
@@ -7349,14 +7333,14 @@
       <c r="B21">
         <v>156000.88360778999</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
       <c r="K21">
         <v>9</v>
       </c>
@@ -7378,14 +7362,14 @@
       <c r="B22">
         <v>156000.15773338001</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
     </row>
     <row r="23" spans="1:16">
       <c r="A23">
@@ -7395,34 +7379,34 @@
       <c r="B23">
         <v>155999.92464208999</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="23">
         <v>8</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="23">
         <f t="shared" ref="D23" si="6">SUM(B23:B25)</f>
         <v>467999.24138626992</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B23:$B25,Import!B23:B25)/$D23</f>
         <v>-97.764264124313669</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B23:$B25,Import!C23:C25)/$D23</f>
         <v>-32.167782985717324</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B23:$B25,Import!D23:D25)/$D23</f>
         <v>39.2655607783934</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B23:$B25,Import!E23:E25)/$D23</f>
         <v>155.03567954368407</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B23:$B25,Import!F23:F25)/$D23</f>
         <v>23.846122984307367</v>
       </c>
-      <c r="J23" s="21">
+      <c r="J23" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B23:$B25,Import!G23:G25)/$D23</f>
         <v>7.846074605933512</v>
       </c>
@@ -7435,14 +7419,14 @@
       <c r="B24">
         <v>155999.65837208999</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
     </row>
     <row r="25" spans="1:16">
       <c r="A25">
@@ -7452,14 +7436,14 @@
       <c r="B25">
         <v>155999.65837208999</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
     </row>
     <row r="26" spans="1:16">
       <c r="A26">
@@ -7469,34 +7453,34 @@
       <c r="B26">
         <v>155999.93463944001</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="23">
         <v>9</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="23">
         <f t="shared" ref="D26" si="7">SUM(B26:B28)</f>
         <v>468000.98061315005</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B26:$B28,Import!B26:B28)/$D26</f>
         <v>-99.814182963562089</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B26:$B28,Import!C26:C28)/$D26</f>
         <v>-32.842064124437279</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B26:$B28,Import!D26:D28)/$D26</f>
         <v>39.284209508678494</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B26:$B28,Import!E26:E28)/$D26</f>
         <v>155.109244290373</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B26:$B28,Import!F26:F28)/$D26</f>
         <v>23.846115288967287</v>
       </c>
-      <c r="J26" s="21">
+      <c r="J26" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B26:$B28,Import!G26:G28)/$D26</f>
         <v>7.8460258897336743</v>
       </c>
@@ -7509,14 +7493,14 @@
       <c r="B27">
         <v>156000.16641352</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
     </row>
     <row r="28" spans="1:16">
       <c r="A28">
@@ -7526,14 +7510,14 @@
       <c r="B28">
         <v>156000.87956018999</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
     </row>
     <row r="29" spans="1:16">
       <c r="A29">
@@ -7543,34 +7527,34 @@
       <c r="B29">
         <v>156000.02019069999</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="23">
         <v>10</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="23">
         <f>SUM(B29:B31)</f>
         <v>467999.82697346993</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B29:$B31,Import!B29:B31)/$D29</f>
         <v>-74.593693830984463</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B29:$B31,Import!C29:C31)/$D29</f>
         <v>-24.543661857522295</v>
       </c>
-      <c r="G29" s="21">
+      <c r="G29" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B29:$B31,Import!D29:D31)/$D29</f>
         <v>39.523201047199258</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B29:$B31,Import!E29:E31)/$D29</f>
         <v>156.05293772728351</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B29:$B31,Import!F29:F31)/$D29</f>
         <v>23.846151722228072</v>
       </c>
-      <c r="J29" s="21">
+      <c r="J29" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B29:$B31,Import!G29:G31)/$D29</f>
         <v>7.8461967836059543</v>
       </c>
@@ -7583,14 +7567,14 @@
       <c r="B30">
         <v>155999.79530150001</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
     </row>
     <row r="31" spans="1:16">
       <c r="A31">
@@ -7600,14 +7584,14 @@
       <c r="B31">
         <v>156000.01148126999</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
     </row>
     <row r="32" spans="1:16">
       <c r="A32">
@@ -7617,7 +7601,7 @@
       <c r="B32" s="6">
         <v>56800.177890960003</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="23">
         <f t="shared" ref="D32" si="8">SUM(B32:B34)</f>
         <v>170400.01192152401</v>
       </c>
@@ -7630,7 +7614,7 @@
       <c r="B33" s="6">
         <v>56799.915072604999</v>
       </c>
-      <c r="D33" s="19"/>
+      <c r="D33" s="23"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
@@ -7640,7 +7624,7 @@
       <c r="B34" s="6">
         <v>56799.918957959002</v>
       </c>
-      <c r="D34" s="19"/>
+      <c r="D34" s="23"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
@@ -7650,7 +7634,7 @@
       <c r="B35" s="6">
         <v>56800.759786957002</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="23">
         <f t="shared" ref="D35" si="9">SUM(B35:B37)</f>
         <v>170399.810101087</v>
       </c>
@@ -7663,7 +7647,7 @@
       <c r="B36" s="6">
         <v>56799.526083912002</v>
       </c>
-      <c r="D36" s="19"/>
+      <c r="D36" s="23"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
@@ -7673,7 +7657,7 @@
       <c r="B37" s="6">
         <v>56799.524230217998</v>
       </c>
-      <c r="D37" s="19"/>
+      <c r="D37" s="23"/>
       <c r="E37" t="s">
         <v>110</v>
       </c>
@@ -7689,18 +7673,18 @@
       <c r="B38" s="3">
         <v>55380.484547013002</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="23">
         <v>1</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="23">
         <f t="shared" ref="D38" si="10">SUM(B38:B40)</f>
         <v>166140.76463097602</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B38:$B40,Import!H38:H40)/$D38</f>
         <v>-82.017769155676746</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B38:$B40,Import!I38:I40)/$D38</f>
         <v>-26.983622857211508</v>
       </c>
@@ -7713,10 +7697,10 @@
       <c r="B39" s="3">
         <v>55379.793729628997</v>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
@@ -7726,10 +7710,10 @@
       <c r="B40" s="3">
         <v>55380.486354334003</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
@@ -7739,18 +7723,18 @@
       <c r="B41" s="3">
         <v>55379.537479976003</v>
       </c>
-      <c r="C41" s="19">
+      <c r="C41" s="23">
         <v>2</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="23">
         <f t="shared" ref="D41" si="11">SUM(B41:B43)</f>
         <v>166139.81620405399</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B41:$B43,Import!H41:H43)/$D41</f>
         <v>-86.243290612191515</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B41:$B43,Import!I41:I43)/$D41</f>
         <v>-28.377602532197205</v>
       </c>
@@ -7763,10 +7747,10 @@
       <c r="B42" s="3">
         <v>55379.537028138002</v>
       </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
@@ -7776,10 +7760,10 @@
       <c r="B43" s="3">
         <v>55380.74169594</v>
       </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
@@ -7789,18 +7773,18 @@
       <c r="B44" s="3">
         <v>48575.594305295999</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C44" s="23">
         <v>3</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="23">
         <f t="shared" ref="D44" si="12">SUM(B44:B46)</f>
         <v>145727.83720381401</v>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B44:$B46,Import!H44:H46)/$D44</f>
         <v>-73.253269173055159</v>
       </c>
-      <c r="F44" s="21">
+      <c r="F44" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B44:$B46,Import!I44:I46)/$D44</f>
         <v>-24.102644923275637</v>
       </c>
@@ -7813,10 +7797,10 @@
       <c r="B45" s="3">
         <v>48576.426997043003</v>
       </c>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
@@ -7826,10 +7810,10 @@
       <c r="B46" s="3">
         <v>48575.815901474998</v>
       </c>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
@@ -7839,18 +7823,18 @@
       <c r="B47" s="3">
         <v>55380.172540020001</v>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="23">
         <v>4</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="23">
         <f t="shared" ref="D47" si="13">SUM(B47:B49)</f>
         <v>166139.91222673102</v>
       </c>
-      <c r="E47" s="21">
+      <c r="E47" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B47:$B49,Import!H47:H49)/$D47</f>
         <v>-84.119613418128338</v>
       </c>
-      <c r="F47" s="21">
+      <c r="F47" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B47:$B49,Import!I47:I49)/$D47</f>
         <v>-27.67864342178029</v>
       </c>
@@ -7863,10 +7847,10 @@
       <c r="B48" s="3">
         <v>55379.917195790003</v>
       </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
@@ -7876,10 +7860,10 @@
       <c r="B49" s="3">
         <v>55379.822490920997</v>
       </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
@@ -7889,18 +7873,18 @@
       <c r="B50" s="3">
         <v>48576.149756432002</v>
       </c>
-      <c r="C50" s="19">
+      <c r="C50" s="23">
         <v>5</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="23">
         <f t="shared" ref="D50" si="14">SUM(B50:B52)</f>
         <v>145728.00449470201</v>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B50:$B52,Import!H50:H52)/$D50</f>
         <v>-73.374714979357705</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B50:$B52,Import!I50:I52)/$D50</f>
         <v>-24.143320649642256</v>
       </c>
@@ -7913,10 +7897,10 @@
       <c r="B51" s="3">
         <v>48575.927369135003</v>
       </c>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
@@ -7926,10 +7910,10 @@
       <c r="B52" s="3">
         <v>48575.927369135003</v>
       </c>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
@@ -7939,18 +7923,18 @@
       <c r="B53" s="3">
         <v>55379.917647625</v>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="23">
         <v>6</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="23">
         <f t="shared" ref="D53" si="15">SUM(B53:B55)</f>
         <v>166140.00376875699</v>
       </c>
-      <c r="E53" s="21">
+      <c r="E53" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B53:$B55,Import!H53:H55)/$D53</f>
         <v>-83.8799059140472</v>
       </c>
-      <c r="F53" s="21">
+      <c r="F53" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B53:$B55,Import!I53:I55)/$D53</f>
         <v>-27.599415532347308</v>
       </c>
@@ -7963,10 +7947,10 @@
       <c r="B54" s="3">
         <v>55380.173443685999</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
@@ -7976,10 +7960,10 @@
       <c r="B55" s="3">
         <v>55379.912677446002</v>
       </c>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
@@ -7989,18 +7973,18 @@
       <c r="B56" s="3">
         <v>48575.927369135003</v>
       </c>
-      <c r="C56" s="19">
+      <c r="C56" s="23">
         <v>7</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="23">
         <f t="shared" ref="D56" si="16">SUM(B56:B58)</f>
         <v>145728.00687262299</v>
       </c>
-      <c r="E56" s="21">
+      <c r="E56" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B56:$B58,Import!H56:H58)/$D56</f>
         <v>-72.454444955151644</v>
       </c>
-      <c r="F56" s="21">
+      <c r="F56" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B56:$B58,Import!I56:I58)/$D56</f>
         <v>-23.839513801626651</v>
       </c>
@@ -8013,10 +7997,10 @@
       <c r="B57" s="3">
         <v>48576.152134352997</v>
       </c>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
@@ -8026,10 +8010,10 @@
       <c r="B58" s="3">
         <v>48575.927369135003</v>
       </c>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
@@ -8039,18 +8023,18 @@
       <c r="B59" s="3">
         <v>48576.006476401002</v>
       </c>
-      <c r="C59" s="19">
+      <c r="C59" s="23">
         <v>8</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="23">
         <f t="shared" ref="D59" si="17">SUM(B59:B61)</f>
         <v>145728.085979889</v>
       </c>
-      <c r="E59" s="21">
+      <c r="E59" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B59:$B61,Import!H59:H61)/$D59</f>
         <v>-73.378352344805009</v>
       </c>
-      <c r="F59" s="21">
+      <c r="F59" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B59:$B61,Import!I59:I61)/$D59</f>
         <v>-24.143365233154984</v>
       </c>
@@ -8063,10 +8047,10 @@
       <c r="B60" s="3">
         <v>48575.927369135003</v>
       </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
@@ -8076,10 +8060,10 @@
       <c r="B61" s="3">
         <v>48576.152134352997</v>
       </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
@@ -8089,18 +8073,18 @@
       <c r="B62" s="3">
         <v>48575.929030533996</v>
       </c>
-      <c r="C62" s="19">
+      <c r="C62" s="23">
         <v>9</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="23">
         <f t="shared" ref="D62" si="18">SUM(B62:B64)</f>
         <v>145728.004570822</v>
       </c>
-      <c r="E62" s="21">
+      <c r="E62" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B62:$B64,Import!H62:H64)/$D62</f>
         <v>-67.390114385738698</v>
       </c>
-      <c r="F62" s="21">
+      <c r="F62" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B62:$B64,Import!I62:I64)/$D62</f>
         <v>-22.173340015479969</v>
       </c>
@@ -8113,10 +8097,10 @@
       <c r="B63" s="3">
         <v>48575.927369135003</v>
       </c>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
@@ -8126,10 +8110,10 @@
       <c r="B64" s="3">
         <v>48576.148171153</v>
       </c>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
@@ -8139,25 +8123,81 @@
     </row>
   </sheetData>
   <mergeCells count="118">
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="E53:E55"/>
-    <mergeCell ref="E56:E58"/>
-    <mergeCell ref="E59:E61"/>
-    <mergeCell ref="E62:E64"/>
-    <mergeCell ref="F38:F40"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="F53:F55"/>
-    <mergeCell ref="F56:F58"/>
-    <mergeCell ref="F59:F61"/>
-    <mergeCell ref="F62:F64"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="J23:J25"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="I26:I28"/>
+    <mergeCell ref="J26:J28"/>
     <mergeCell ref="F29:F31"/>
     <mergeCell ref="G29:G31"/>
     <mergeCell ref="H29:H31"/>
@@ -8182,81 +8222,25 @@
     <mergeCell ref="C41:C43"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="C47:C49"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="J23:J25"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="H26:H28"/>
-    <mergeCell ref="I26:I28"/>
-    <mergeCell ref="J26:J28"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="E56:E58"/>
+    <mergeCell ref="E59:E61"/>
+    <mergeCell ref="E62:E64"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="F53:F55"/>
+    <mergeCell ref="F56:F58"/>
+    <mergeCell ref="F59:F61"/>
+    <mergeCell ref="F62:F64"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8318,25 +8302,25 @@
       <c r="O1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
       <c r="W1" t="s">
         <v>42</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Y1" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="21"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
       <c r="AE1" t="s">
         <v>44</v>
       </c>
@@ -8366,2164 +8350,2164 @@
       </c>
     </row>
     <row r="2" spans="1:43">
-      <c r="A2" s="19">
+      <c r="A2" s="23">
         <f>'Results_e,f'!C2</f>
         <v>1</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="23">
         <f>'Results_e,f'!E2</f>
-        <v>-70.752968545441874</v>
-      </c>
-      <c r="C2" s="19">
+        <v>-55.413272966050641</v>
+      </c>
+      <c r="C2" s="23">
         <f>'Results_e,f'!F2</f>
         <v>-23.279955056006532</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="23">
         <f>'Results_e,f'!G2</f>
         <v>39.399464897236562</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="23">
         <f>'Results_e,f'!H2</f>
         <v>155.56517208700083</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="23">
         <f>'Results_e,f'!I2</f>
         <v>23.846147653298427</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G2" s="23">
         <f>'Results_e,f'!J2</f>
         <v>7.8462151433468197</v>
       </c>
-      <c r="I2" s="19">
+      <c r="I2" s="23">
         <f>MAX(-MIN(B2,0),-MIN(F2,0))</f>
-        <v>70.752968545441874</v>
-      </c>
-      <c r="J2" s="19">
+        <v>55.413272966050641</v>
+      </c>
+      <c r="J2" s="23">
         <f>IF(-MIN(B2,0)&gt;=-MIN(F2,0),F2,B2)</f>
         <v>23.846147653298427</v>
       </c>
-      <c r="K2" s="19">
+      <c r="K2" s="23">
         <f>MAX(-MIN(C2,0),-MIN(G2,0))</f>
         <v>23.279955056006532</v>
       </c>
-      <c r="L2" s="19">
+      <c r="L2" s="23">
         <f>IF(-MIN(C2,0)&gt;=-MIN(G2,0),G2,C2)</f>
         <v>7.8462151433468197</v>
       </c>
-      <c r="N2" s="19">
+      <c r="N2" s="23">
         <f>IF(J2&gt;0,-J2/I2,ABS(J2)/I2)</f>
-        <v>-0.33703388201984735</v>
-      </c>
-      <c r="O2" s="19">
+        <v>-0.43033277727355951</v>
+      </c>
+      <c r="O2" s="23">
         <f>IF(L2&gt;0,-L2/K2,ABS(L2)/K2)</f>
         <v>-0.33703738364058372</v>
       </c>
-      <c r="Q2" s="19">
+      <c r="Q2" s="23">
         <f xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$N2*$B$40^2))</f>
-        <v>-5.4645571859300714</v>
-      </c>
-      <c r="R2" s="19">
+        <v>-3.8674314186628855</v>
+      </c>
+      <c r="R2" s="23">
         <f t="shared" ref="R2:V2" si="0" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N2*$B$40^2))</f>
-        <v>19.424716768903426</v>
-      </c>
-      <c r="S2" s="19">
+        <v>147.85069175888054</v>
+      </c>
+      <c r="S2" s="23">
         <f xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N2*$B$40^2))</f>
-        <v>6.0334908399040517</v>
-      </c>
-      <c r="T2" s="19">
+        <v>7.0216432338443271</v>
+      </c>
+      <c r="T2" s="23">
         <f xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N2*$B$40^2))</f>
-        <v>5.3556009540869001</v>
-      </c>
-      <c r="U2" s="19">
+        <v>5.7264299320778802</v>
+      </c>
+      <c r="U2" s="23">
         <f xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N2*$B$40^2))</f>
-        <v>5.8472357395120342</v>
-      </c>
-      <c r="V2" s="19">
+        <v>6.0796333610398294</v>
+      </c>
+      <c r="V2" s="23">
         <f t="shared" si="0"/>
-        <v>6.8250699555434595</v>
-      </c>
-      <c r="W2" s="21">
+        <v>7.0034539468655286</v>
+      </c>
+      <c r="W2" s="24">
         <f>_xlfn.MINIFS(Q2:V2,Q2:V2,"&gt;0")</f>
-        <v>5.3556009540869001</v>
-      </c>
-      <c r="Y2" s="19">
+        <v>5.7264299320778802</v>
+      </c>
+      <c r="Y2" s="23">
         <f xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O2*$B$40^2))</f>
         <v>-5.4644724910137024</v>
       </c>
-      <c r="Z2" s="19">
+      <c r="Z2" s="23">
         <f t="shared" ref="Z2:AD2" si="1" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O2*$B$40^2))</f>
         <v>19.425350041898028</v>
       </c>
-      <c r="AA2" s="19">
+      <c r="AA2" s="23">
         <f t="shared" si="1"/>
         <v>6.0335227074575402</v>
       </c>
-      <c r="AB2" s="19">
+      <c r="AB2" s="23">
         <f t="shared" si="1"/>
         <v>5.3556139705077852</v>
       </c>
-      <c r="AC2" s="19">
+      <c r="AC2" s="23">
         <f t="shared" si="1"/>
         <v>5.8472441282788052</v>
       </c>
-      <c r="AD2" s="19">
+      <c r="AD2" s="23">
         <f t="shared" si="1"/>
         <v>6.8250764799907406</v>
       </c>
-      <c r="AE2" s="21">
+      <c r="AE2" s="24">
         <f>_xlfn.MINIFS(Y2:AD2,Y2:AD2,"&gt;0")</f>
         <v>5.3556139705077852</v>
       </c>
-      <c r="AG2" s="19">
+      <c r="AG2" s="23">
         <f>W2*$B$41</f>
-        <v>124.31967138687214</v>
-      </c>
-      <c r="AH2" s="19">
+        <v>132.92773182300081</v>
+      </c>
+      <c r="AH2" s="23">
         <f>AE2*$B$41</f>
         <v>124.31997353730885</v>
       </c>
-      <c r="AJ2" s="19">
+      <c r="AJ2" s="23">
         <f>1.5*I2 / AG2</f>
-        <v>0.85368189630985314</v>
-      </c>
-      <c r="AK2" s="19">
+        <v>0.62530149509926058</v>
+      </c>
+      <c r="AK2" s="23">
         <f>1.5*K2 / AH2</f>
         <v>0.28088754839969626</v>
       </c>
-      <c r="AM2" s="19">
+      <c r="AM2" s="23">
         <f>ABS((D2*1.5) / $B$43)</f>
         <v>0.44013741150871188</v>
       </c>
-      <c r="AN2" s="19">
+      <c r="AN2" s="23">
         <f>ABS((E2*1.5) / $B$43)</f>
         <v>1.7378421849602905</v>
       </c>
-      <c r="AP2" s="21">
+      <c r="AP2" s="24">
         <f>1/((AJ2)+(AM2)^2)</f>
-        <v>0.95474249674484579</v>
-      </c>
-      <c r="AQ2" s="21">
+        <v>1.2209677731796567</v>
+      </c>
+      <c r="AQ2" s="24">
         <f>1/((AK2)+(AN2)^2)</f>
         <v>0.30294006285631753</v>
       </c>
     </row>
     <row r="3" spans="1:43">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19"/>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
-      <c r="W3" s="21"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="19"/>
-      <c r="AC3" s="19"/>
-      <c r="AD3" s="19"/>
-      <c r="AE3" s="21"/>
-      <c r="AG3" s="19"/>
-      <c r="AH3" s="19"/>
-      <c r="AJ3" s="19"/>
-      <c r="AK3" s="19"/>
-      <c r="AM3" s="19"/>
-      <c r="AN3" s="19"/>
-      <c r="AP3" s="21"/>
-      <c r="AQ3" s="21"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="24"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="23"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="24"/>
+      <c r="AG3" s="23"/>
+      <c r="AH3" s="23"/>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AP3" s="24"/>
+      <c r="AQ3" s="24"/>
     </row>
     <row r="4" spans="1:43">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="21"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="19"/>
-      <c r="AE4" s="21"/>
-      <c r="AG4" s="19"/>
-      <c r="AH4" s="19"/>
-      <c r="AJ4" s="19"/>
-      <c r="AK4" s="19"/>
-      <c r="AM4" s="19"/>
-      <c r="AN4" s="19"/>
-      <c r="AP4" s="21"/>
-      <c r="AQ4" s="21"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="24"/>
+      <c r="Y4" s="23"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="23"/>
+      <c r="AC4" s="23"/>
+      <c r="AD4" s="23"/>
+      <c r="AE4" s="24"/>
+      <c r="AG4" s="23"/>
+      <c r="AH4" s="23"/>
+      <c r="AJ4" s="23"/>
+      <c r="AK4" s="23"/>
+      <c r="AM4" s="23"/>
+      <c r="AN4" s="23"/>
+      <c r="AP4" s="24"/>
+      <c r="AQ4" s="24"/>
     </row>
     <row r="5" spans="1:43">
-      <c r="A5" s="19">
+      <c r="A5" s="23">
         <f>'Results_e,f'!C5</f>
         <v>2</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="23">
         <f>'Results_e,f'!E5</f>
         <v>-91.457956292773275</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="23">
         <f>'Results_e,f'!F5</f>
         <v>-30.092478229483675</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="23">
         <f>'Results_e,f'!G5</f>
         <v>39.032756873157155</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="23">
         <f>'Results_e,f'!H5</f>
         <v>154.11746042478134</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="23">
         <f>'Results_e,f'!I5</f>
         <v>23.846152654191794</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="23">
         <f>'Results_e,f'!J5</f>
         <v>7.8462545426913328</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="23">
         <f t="shared" ref="I5" si="2">MAX(-MIN(B5,0),-MIN(F5,0))</f>
         <v>91.457956292773275</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="23">
         <f t="shared" ref="J5" si="3">IF(-MIN(B5,0)&gt;=-MIN(F5,0),F5,B5)</f>
         <v>23.846152654191794</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="23">
         <f t="shared" ref="K5" si="4">MAX(-MIN(C5,0),-MIN(G5,0))</f>
         <v>30.092478229483675</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="23">
         <f t="shared" ref="L5" si="5">IF(-MIN(C5,0)&gt;=-MIN(G5,0),G5,C5)</f>
         <v>7.8462545426913328</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="23">
         <f>IF(J5&gt;0,-J5/I5,ABS(J5)/I5)</f>
         <v>-0.26073349570436488</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="23">
         <f t="shared" ref="O5" si="6">IF(L5&gt;0,-L5/K5,ABS(L5)/K5)</f>
         <v>-0.26073806493623436</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="23">
         <f xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$N5*$B$40^2))</f>
         <v>-8.2512246051332667</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="23">
         <f t="shared" ref="R5:V5" si="7" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N5*$B$40^2))</f>
         <v>11.357078973220895</v>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="23">
         <f t="shared" si="7"/>
         <v>5.4107686155903352</v>
       </c>
-      <c r="T5" s="19">
+      <c r="T5" s="23">
         <f t="shared" si="7"/>
         <v>5.0862387300719893</v>
       </c>
-      <c r="U5" s="19">
+      <c r="U5" s="23">
         <f t="shared" si="7"/>
         <v>5.6699856414585534</v>
       </c>
-      <c r="V5" s="19">
+      <c r="V5" s="23">
         <f t="shared" si="7"/>
         <v>6.6858032106778769</v>
       </c>
-      <c r="W5" s="21">
+      <c r="W5" s="24">
         <f t="shared" ref="W5" si="8">_xlfn.MINIFS(Q5:V5,Q5:V5,"&gt;0")</f>
         <v>5.0862387300719893</v>
       </c>
-      <c r="Y5" s="19">
+      <c r="Y5" s="23">
         <f t="shared" ref="Y5" si="9" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O5*$B$40^2))</f>
         <v>-8.2509726334298765</v>
       </c>
-      <c r="Z5" s="19">
+      <c r="Z5" s="23">
         <f t="shared" ref="Z5" si="10" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O5*$B$40^2))</f>
         <v>11.35736145185516</v>
       </c>
-      <c r="AA5" s="19">
+      <c r="AA5" s="23">
         <f t="shared" ref="AA5" si="11" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O5*$B$40^2))</f>
         <v>5.4108020584814458</v>
       </c>
-      <c r="AB5" s="19">
+      <c r="AB5" s="23">
         <f t="shared" ref="AB5" si="12" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O5*$B$40^2))</f>
         <v>5.0862540495154462</v>
       </c>
-      <c r="AC5" s="19">
+      <c r="AC5" s="23">
         <f t="shared" ref="AC5" si="13" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O5*$B$40^2))</f>
         <v>5.6699959342953976</v>
       </c>
-      <c r="AD5" s="19">
+      <c r="AD5" s="23">
         <f t="shared" ref="AD5" si="14" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O5*$B$40^2))</f>
         <v>6.6858113804679675</v>
       </c>
-      <c r="AE5" s="21">
+      <c r="AE5" s="24">
         <f t="shared" ref="AE5" si="15">_xlfn.MINIFS(Y5:AD5,Y5:AD5,"&gt;0")</f>
         <v>5.0862540495154462</v>
       </c>
-      <c r="AG5" s="19">
+      <c r="AG5" s="23">
         <f t="shared" ref="AG5" si="16">W5*$B$41</f>
         <v>118.06696072738649</v>
       </c>
-      <c r="AH5" s="19">
+      <c r="AH5" s="23">
         <f>AE5*$B$41</f>
         <v>118.06731633793191</v>
       </c>
-      <c r="AJ5" s="19">
+      <c r="AJ5" s="23">
         <f t="shared" ref="AJ5" si="17">1.5*I5 / AG5</f>
         <v>1.1619417794273621</v>
       </c>
-      <c r="AK5" s="19">
+      <c r="AK5" s="23">
         <f t="shared" ref="AK5" si="18">1.5*K5 / AH5</f>
         <v>0.38231340174642076</v>
       </c>
-      <c r="AM5" s="19">
+      <c r="AM5" s="23">
         <f t="shared" ref="AM5:AN5" si="19">ABS((D5*1.5) / $B$43)</f>
         <v>0.43604086042816392</v>
       </c>
-      <c r="AN5" s="19">
+      <c r="AN5" s="23">
         <f t="shared" si="19"/>
         <v>1.7216695779139204</v>
       </c>
-      <c r="AP5" s="21">
+      <c r="AP5" s="24">
         <f t="shared" ref="AP5:AQ5" si="20">1/((AJ5)+(AM5)^2)</f>
         <v>0.73960481108176712</v>
       </c>
-      <c r="AQ5" s="21">
+      <c r="AQ5" s="24">
         <f t="shared" si="20"/>
         <v>0.2988232754245585</v>
       </c>
     </row>
     <row r="6" spans="1:43">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="21"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="21"/>
-      <c r="AG6" s="19"/>
-      <c r="AH6" s="19"/>
-      <c r="AJ6" s="19"/>
-      <c r="AK6" s="19"/>
-      <c r="AM6" s="19"/>
-      <c r="AN6" s="19"/>
-      <c r="AP6" s="21"/>
-      <c r="AQ6" s="21"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="23"/>
+      <c r="W6" s="24"/>
+      <c r="Y6" s="23"/>
+      <c r="Z6" s="23"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="23"/>
+      <c r="AC6" s="23"/>
+      <c r="AD6" s="23"/>
+      <c r="AE6" s="24"/>
+      <c r="AG6" s="23"/>
+      <c r="AH6" s="23"/>
+      <c r="AJ6" s="23"/>
+      <c r="AK6" s="23"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="23"/>
+      <c r="AP6" s="24"/>
+      <c r="AQ6" s="24"/>
     </row>
     <row r="7" spans="1:43">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="21"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="21"/>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
-      <c r="AJ7" s="19"/>
-      <c r="AK7" s="19"/>
-      <c r="AM7" s="19"/>
-      <c r="AN7" s="19"/>
-      <c r="AP7" s="21"/>
-      <c r="AQ7" s="21"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="23"/>
+      <c r="W7" s="24"/>
+      <c r="Y7" s="23"/>
+      <c r="Z7" s="23"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="23"/>
+      <c r="AD7" s="23"/>
+      <c r="AE7" s="24"/>
+      <c r="AG7" s="23"/>
+      <c r="AH7" s="23"/>
+      <c r="AJ7" s="23"/>
+      <c r="AK7" s="23"/>
+      <c r="AM7" s="23"/>
+      <c r="AN7" s="23"/>
+      <c r="AP7" s="24"/>
+      <c r="AQ7" s="24"/>
     </row>
     <row r="8" spans="1:43">
-      <c r="A8" s="19">
+      <c r="A8" s="23">
         <f>'Results_e,f'!C8</f>
         <v>3</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="23">
         <f>'Results_e,f'!E8</f>
         <v>-93.462360205020303</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="23">
         <f>'Results_e,f'!F8</f>
         <v>-30.752011325182355</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="23">
         <f>'Results_e,f'!G8</f>
         <v>39.135793297071388</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="23">
         <f>'Results_e,f'!H8</f>
         <v>154.52201225594342</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="23">
         <f>'Results_e,f'!I8</f>
         <v>23.846018873279803</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="23">
         <f>'Results_e,f'!J8</f>
         <v>7.8456136776305456</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="23">
         <f t="shared" ref="I8" si="21">MAX(-MIN(B8,0),-MIN(F8,0))</f>
         <v>93.462360205020303</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="23">
         <f t="shared" ref="J8" si="22">IF(-MIN(B8,0)&gt;=-MIN(F8,0),F8,B8)</f>
         <v>23.846018873279803</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="23">
         <f t="shared" ref="K8" si="23">MAX(-MIN(C8,0),-MIN(G8,0))</f>
         <v>30.752011325182355</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="23">
         <f t="shared" ref="L8" si="24">IF(-MIN(C8,0)&gt;=-MIN(G8,0),G8,C8)</f>
         <v>7.8456136776305456</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="23">
         <f t="shared" ref="N8" si="25">IF(J8&gt;0,-J8/I8,ABS(J8)/I8)</f>
         <v>-0.25514034549278292</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="23">
         <f t="shared" ref="O8" si="26">IF(L8&gt;0,-L8/K8,ABS(L8)/K8)</f>
         <v>-0.25512522074307026</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="23">
         <f t="shared" ref="Q8:Q17" si="27" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$N8*$B$40^2))</f>
         <v>-8.5716480167006353</v>
       </c>
-      <c r="R8" s="19">
+      <c r="R8" s="23">
         <f t="shared" ref="R8" si="28" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N8*$B$40^2))</f>
         <v>11.021524439463844</v>
       </c>
-      <c r="S8" s="19">
+      <c r="S8" s="23">
         <f t="shared" ref="S8" si="29" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N8*$B$40^2))</f>
         <v>5.3701391608413971</v>
       </c>
-      <c r="T8" s="19">
+      <c r="T8" s="23">
         <f t="shared" ref="T8" si="30" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N8*$B$40^2))</f>
         <v>5.0675552952462963</v>
       </c>
-      <c r="U8" s="19">
+      <c r="U8" s="23">
         <f t="shared" ref="U8" si="31" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N8*$B$40^2))</f>
         <v>5.6574142425788247</v>
       </c>
-      <c r="V8" s="19">
+      <c r="V8" s="23">
         <f t="shared" ref="V8" si="32" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$N8*$B$40^2))</f>
         <v>6.6758176023794746</v>
       </c>
-      <c r="W8" s="21">
+      <c r="W8" s="24">
         <f t="shared" ref="W8" si="33">_xlfn.MINIFS(Q8:V8,Q8:V8,"&gt;0")</f>
         <v>5.0675552952462963</v>
       </c>
-      <c r="Y8" s="19">
+      <c r="Y8" s="23">
         <f t="shared" ref="Y8" si="34" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O8*$B$40^2))</f>
         <v>-8.5725482342641008</v>
       </c>
-      <c r="Z8" s="19">
+      <c r="Z8" s="23">
         <f t="shared" ref="Z8" si="35" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O8*$B$40^2))</f>
         <v>11.020643927726368</v>
       </c>
-      <c r="AA8" s="19">
+      <c r="AA8" s="23">
         <f t="shared" ref="AA8" si="36" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O8*$B$40^2))</f>
         <v>5.370030119680397</v>
       </c>
-      <c r="AB8" s="19">
+      <c r="AB8" s="23">
         <f t="shared" ref="AB8" si="37" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O8*$B$40^2))</f>
         <v>5.0675049584145997</v>
       </c>
-      <c r="AC8" s="19">
+      <c r="AC8" s="23">
         <f t="shared" ref="AC8" si="38" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O8*$B$40^2))</f>
         <v>5.6573803231339124</v>
       </c>
-      <c r="AD8" s="19">
+      <c r="AD8" s="23">
         <f t="shared" ref="AD8" si="39" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O8*$B$40^2))</f>
         <v>6.6757906401774481</v>
       </c>
-      <c r="AE8" s="21">
+      <c r="AE8" s="24">
         <f t="shared" ref="AE8" si="40">_xlfn.MINIFS(Y8:AD8,Y8:AD8,"&gt;0")</f>
         <v>5.0675049584145997</v>
       </c>
-      <c r="AG8" s="19">
+      <c r="AG8" s="23">
         <f t="shared" ref="AG8" si="41">W8*$B$41</f>
         <v>117.63326178345459</v>
       </c>
-      <c r="AH8" s="19">
+      <c r="AH8" s="23">
         <f t="shared" ref="AH8" si="42">AE8*$B$41</f>
         <v>117.63209331357999</v>
       </c>
-      <c r="AJ8" s="19">
+      <c r="AJ8" s="23">
         <f t="shared" ref="AJ8" si="43">1.5*I8 / AG8</f>
         <v>1.1917848589934197</v>
       </c>
-      <c r="AK8" s="19">
+      <c r="AK8" s="23">
         <f t="shared" ref="AK8" si="44">1.5*K8 / AH8</f>
         <v>0.39213802703320849</v>
       </c>
-      <c r="AM8" s="19">
+      <c r="AM8" s="23">
         <f t="shared" ref="AM8:AN8" si="45">ABS((D8*1.5) / $B$43)</f>
         <v>0.43719189598235253</v>
       </c>
-      <c r="AN8" s="19">
+      <c r="AN8" s="23">
         <f t="shared" si="45"/>
         <v>1.7261888879160538</v>
       </c>
-      <c r="AP8" s="21">
+      <c r="AP8" s="24">
         <f t="shared" ref="AP8:AQ8" si="46">1/((AJ8)+(AM8)^2)</f>
         <v>0.72310678397642913</v>
       </c>
-      <c r="AQ8" s="21">
+      <c r="AQ8" s="24">
         <f t="shared" si="46"/>
         <v>0.29657168144179852</v>
       </c>
     </row>
     <row r="9" spans="1:43">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="21"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="21"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AP9" s="21"/>
-      <c r="AQ9" s="21"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="24"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
+      <c r="AE9" s="24"/>
+      <c r="AG9" s="23"/>
+      <c r="AH9" s="23"/>
+      <c r="AJ9" s="23"/>
+      <c r="AK9" s="23"/>
+      <c r="AM9" s="23"/>
+      <c r="AN9" s="23"/>
+      <c r="AP9" s="24"/>
+      <c r="AQ9" s="24"/>
     </row>
     <row r="10" spans="1:43">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="21"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="21"/>
-      <c r="AG10" s="19"/>
-      <c r="AH10" s="19"/>
-      <c r="AJ10" s="19"/>
-      <c r="AK10" s="19"/>
-      <c r="AM10" s="19"/>
-      <c r="AN10" s="19"/>
-      <c r="AP10" s="21"/>
-      <c r="AQ10" s="21"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="24"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="23"/>
+      <c r="AC10" s="23"/>
+      <c r="AD10" s="23"/>
+      <c r="AE10" s="24"/>
+      <c r="AG10" s="23"/>
+      <c r="AH10" s="23"/>
+      <c r="AJ10" s="23"/>
+      <c r="AK10" s="23"/>
+      <c r="AM10" s="23"/>
+      <c r="AN10" s="23"/>
+      <c r="AP10" s="24"/>
+      <c r="AQ10" s="24"/>
     </row>
     <row r="11" spans="1:43">
-      <c r="A11" s="19">
+      <c r="A11" s="23">
         <f>'Results_e,f'!C11</f>
         <v>4</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="23">
         <f>'Results_e,f'!E11</f>
         <v>-93.222038415665409</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="23">
         <f>'Results_e,f'!F11</f>
         <v>-30.673498199284161</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="23">
         <f>'Results_e,f'!G11</f>
         <v>39.14346902990939</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="23">
         <f>'Results_e,f'!H11</f>
         <v>154.55405316501287</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="23">
         <f>'Results_e,f'!I11</f>
         <v>23.846320774572309</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="23">
         <f>'Results_e,f'!J11</f>
         <v>7.8467995813713021</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="23">
         <f t="shared" ref="I11" si="47">MAX(-MIN(B11,0),-MIN(F11,0))</f>
         <v>93.222038415665409</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="23">
         <f t="shared" ref="J11" si="48">IF(-MIN(B11,0)&gt;=-MIN(F11,0),F11,B11)</f>
         <v>23.846320774572309</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="23">
         <f t="shared" ref="K11" si="49">MAX(-MIN(C11,0),-MIN(G11,0))</f>
         <v>30.673498199284161</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="23">
         <f t="shared" ref="L11" si="50">IF(-MIN(C11,0)&gt;=-MIN(G11,0),G11,C11)</f>
         <v>7.8467995813713021</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="23">
         <f t="shared" ref="N11" si="51">IF(J11&gt;0,-J11/I11,ABS(J11)/I11)</f>
         <v>-0.25580132316185306</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="23">
         <f t="shared" ref="O11" si="52">IF(L11&gt;0,-L11/K11,ABS(L11)/K11)</f>
         <v>-0.2558169117324357</v>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="23">
         <f t="shared" si="27"/>
         <v>-8.5324907866028461</v>
       </c>
-      <c r="R11" s="19">
+      <c r="R11" s="23">
         <f t="shared" ref="R11" si="53" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N11*$B$40^2))</f>
         <v>11.060142235247046</v>
       </c>
-      <c r="S11" s="19">
+      <c r="S11" s="23">
         <f t="shared" ref="S11" si="54" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N11*$B$40^2))</f>
         <v>5.3749087770414636</v>
       </c>
-      <c r="T11" s="19">
+      <c r="T11" s="23">
         <f t="shared" ref="T11" si="55" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N11*$B$40^2))</f>
         <v>5.0697560788896814</v>
       </c>
-      <c r="U11" s="19">
+      <c r="U11" s="23">
         <f t="shared" ref="U11" si="56" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N11*$B$40^2))</f>
         <v>5.6588969782610627</v>
       </c>
-      <c r="V11" s="19">
+      <c r="V11" s="23">
         <f t="shared" ref="V11" si="57" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$N11*$B$40^2))</f>
         <v>6.6769961099157484</v>
       </c>
-      <c r="W11" s="21">
+      <c r="W11" s="24">
         <f t="shared" ref="W11" si="58">_xlfn.MINIFS(Q11:V11,Q11:V11,"&gt;0")</f>
         <v>5.0697560788896814</v>
       </c>
-      <c r="Y11" s="19">
+      <c r="Y11" s="23">
         <f t="shared" ref="Y11" si="59" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O11*$B$40^2))</f>
         <v>-8.5315716158833492</v>
       </c>
-      <c r="Z11" s="19">
+      <c r="Z11" s="23">
         <f t="shared" ref="Z11" si="60" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O11*$B$40^2))</f>
         <v>11.061056268343959</v>
       </c>
-      <c r="AA11" s="19">
+      <c r="AA11" s="23">
         <f t="shared" ref="AA11" si="61" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O11*$B$40^2))</f>
         <v>5.3750213664649102</v>
       </c>
-      <c r="AB11" s="19">
+      <c r="AB11" s="23">
         <f t="shared" ref="AB11" si="62" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O11*$B$40^2))</f>
         <v>5.0698080054879497</v>
       </c>
-      <c r="AC11" s="19">
+      <c r="AC11" s="23">
         <f t="shared" ref="AC11" si="63" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O11*$B$40^2))</f>
         <v>5.6589319566448095</v>
       </c>
-      <c r="AD11" s="19">
+      <c r="AD11" s="23">
         <f t="shared" ref="AD11" si="64" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O11*$B$40^2))</f>
         <v>6.6770239089903898</v>
       </c>
-      <c r="AE11" s="21">
+      <c r="AE11" s="24">
         <f t="shared" ref="AE11" si="65">_xlfn.MINIFS(Y11:AD11,Y11:AD11,"&gt;0")</f>
         <v>5.0698080054879497</v>
       </c>
-      <c r="AG11" s="19">
+      <c r="AG11" s="23">
         <f t="shared" ref="AG11" si="66">W11*$B$41</f>
         <v>117.68434861790786</v>
       </c>
-      <c r="AH11" s="19">
+      <c r="AH11" s="23">
         <f t="shared" ref="AH11" si="67">AE11*$B$41</f>
         <v>117.68555399106548</v>
       </c>
-      <c r="AJ11" s="19">
+      <c r="AJ11" s="23">
         <f t="shared" ref="AJ11" si="68">1.5*I11 / AG11</f>
         <v>1.188204372677472</v>
       </c>
-      <c r="AK11" s="19">
+      <c r="AK11" s="23">
         <f t="shared" ref="AK11" si="69">1.5*K11 / AH11</f>
         <v>0.39095917670931202</v>
       </c>
-      <c r="AM11" s="19">
+      <c r="AM11" s="23">
         <f t="shared" ref="AM11:AN11" si="70">ABS((D11*1.5) / $B$43)</f>
         <v>0.4372776427606796</v>
       </c>
-      <c r="AN11" s="19">
+      <c r="AN11" s="23">
         <f t="shared" si="70"/>
         <v>1.7265468217818309</v>
       </c>
-      <c r="AP11" s="21">
+      <c r="AP11" s="24">
         <f t="shared" ref="AP11:AQ11" si="71">1/((AJ11)+(AM11)^2)</f>
         <v>0.72494441168771973</v>
       </c>
-      <c r="AQ11" s="21">
+      <c r="AQ11" s="24">
         <f t="shared" si="71"/>
         <v>0.29656666804211013</v>
       </c>
     </row>
     <row r="12" spans="1:43">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="21"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="21"/>
-      <c r="AG12" s="19"/>
-      <c r="AH12" s="19"/>
-      <c r="AJ12" s="19"/>
-      <c r="AK12" s="19"/>
-      <c r="AM12" s="19"/>
-      <c r="AN12" s="19"/>
-      <c r="AP12" s="21"/>
-      <c r="AQ12" s="21"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="24"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+      <c r="AC12" s="23"/>
+      <c r="AD12" s="23"/>
+      <c r="AE12" s="24"/>
+      <c r="AG12" s="23"/>
+      <c r="AH12" s="23"/>
+      <c r="AJ12" s="23"/>
+      <c r="AK12" s="23"/>
+      <c r="AM12" s="23"/>
+      <c r="AN12" s="23"/>
+      <c r="AP12" s="24"/>
+      <c r="AQ12" s="24"/>
     </row>
     <row r="13" spans="1:43">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="21"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="21"/>
-      <c r="AG13" s="19"/>
-      <c r="AH13" s="19"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
-      <c r="AM13" s="19"/>
-      <c r="AN13" s="19"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="24"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="23"/>
+      <c r="AD13" s="23"/>
+      <c r="AE13" s="24"/>
+      <c r="AG13" s="23"/>
+      <c r="AH13" s="23"/>
+      <c r="AJ13" s="23"/>
+      <c r="AK13" s="23"/>
+      <c r="AM13" s="23"/>
+      <c r="AN13" s="23"/>
+      <c r="AP13" s="24"/>
+      <c r="AQ13" s="24"/>
     </row>
     <row r="14" spans="1:43">
-      <c r="A14" s="19">
+      <c r="A14" s="23">
         <f>'Results_e,f'!C14</f>
         <v>5</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="23">
         <f>'Results_e,f'!E14</f>
         <v>-92.821111081150789</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="23">
         <f>'Results_e,f'!F14</f>
         <v>-30.540989580149905</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="23">
         <f>'Results_e,f'!G14</f>
         <v>39.142242190929672</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="23">
         <f>'Results_e,f'!H14</f>
         <v>154.54799228379497</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="23">
         <f>'Results_e,f'!I14</f>
         <v>23.846146263511852</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="23">
         <f>'Results_e,f'!J14</f>
         <v>7.8461398628633692</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="23">
         <f t="shared" ref="I14" si="72">MAX(-MIN(B14,0),-MIN(F14,0))</f>
         <v>92.821111081150789</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="23">
         <f t="shared" ref="J14" si="73">IF(-MIN(B14,0)&gt;=-MIN(F14,0),F14,B14)</f>
         <v>23.846146263511852</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="23">
         <f t="shared" ref="K14" si="74">MAX(-MIN(C14,0),-MIN(G14,0))</f>
         <v>30.540989580149905</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="23">
         <f t="shared" ref="L14" si="75">IF(-MIN(C14,0)&gt;=-MIN(G14,0),G14,C14)</f>
         <v>7.8461398628633692</v>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="23">
         <f t="shared" ref="N14" si="76">IF(J14&gt;0,-J14/I14,ABS(J14)/I14)</f>
         <v>-0.25690433981838312</v>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="23">
         <f t="shared" ref="O14" si="77">IF(L14&gt;0,-L14/K14,ABS(L14)/K14)</f>
         <v>-0.25690522706451407</v>
       </c>
-      <c r="Q14" s="19">
+      <c r="Q14" s="23">
         <f t="shared" si="27"/>
         <v>-8.4679371750067354</v>
       </c>
-      <c r="R14" s="19">
+      <c r="R14" s="23">
         <f t="shared" ref="R14" si="78" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N14*$B$40^2))</f>
         <v>11.125192434154602</v>
       </c>
-      <c r="S14" s="19">
+      <c r="S14" s="23">
         <f t="shared" ref="S14" si="79" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N14*$B$40^2))</f>
         <v>5.3828870417872938</v>
       </c>
-      <c r="T14" s="19">
+      <c r="T14" s="23">
         <f t="shared" ref="T14" si="80" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N14*$B$40^2))</f>
         <v>5.073432930138436</v>
       </c>
-      <c r="U14" s="19">
+      <c r="U14" s="23">
         <f t="shared" ref="U14" si="81" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N14*$B$40^2))</f>
         <v>5.661373047678361</v>
       </c>
-      <c r="V14" s="19">
+      <c r="V14" s="23">
         <f t="shared" ref="V14" si="82" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$N14*$B$40^2))</f>
         <v>6.6789636893188531</v>
       </c>
-      <c r="W14" s="21">
+      <c r="W14" s="24">
         <f t="shared" ref="W14" si="83">_xlfn.MINIFS(Q14:V14,Q14:V14,"&gt;0")</f>
         <v>5.073432930138436</v>
       </c>
-      <c r="Y14" s="19">
+      <c r="Y14" s="23">
         <f t="shared" ref="Y14" si="84" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O14*$B$40^2))</f>
         <v>-8.4678856424435285</v>
       </c>
-      <c r="Z14" s="19">
+      <c r="Z14" s="23">
         <f t="shared" ref="Z14" si="85" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O14*$B$40^2))</f>
         <v>11.125245067326912</v>
       </c>
-      <c r="AA14" s="19">
+      <c r="AA14" s="23">
         <f t="shared" ref="AA14" si="86" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O14*$B$40^2))</f>
         <v>5.3828934688890246</v>
       </c>
-      <c r="AB14" s="19">
+      <c r="AB14" s="23">
         <f t="shared" ref="AB14" si="87" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O14*$B$40^2))</f>
         <v>5.0734358898760794</v>
       </c>
-      <c r="AC14" s="19">
+      <c r="AC14" s="23">
         <f t="shared" ref="AC14" si="88" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O14*$B$40^2))</f>
         <v>5.6613750402548328</v>
       </c>
-      <c r="AD14" s="19">
+      <c r="AD14" s="23">
         <f t="shared" ref="AD14" si="89" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O14*$B$40^2))</f>
         <v>6.6789652724699753</v>
       </c>
-      <c r="AE14" s="21">
+      <c r="AE14" s="24">
         <f t="shared" ref="AE14" si="90">_xlfn.MINIFS(Y14:AD14,Y14:AD14,"&gt;0")</f>
         <v>5.0734358898760794</v>
       </c>
-      <c r="AG14" s="19">
+      <c r="AG14" s="23">
         <f t="shared" ref="AG14" si="91">W14*$B$41</f>
         <v>117.76969943902061</v>
       </c>
-      <c r="AH14" s="19">
+      <c r="AH14" s="23">
         <f t="shared" ref="AH14" si="92">AE14*$B$41</f>
         <v>117.76976814346935</v>
       </c>
-      <c r="AJ14" s="19">
+      <c r="AJ14" s="23">
         <f t="shared" ref="AJ14" si="93">1.5*I14 / AG14</f>
         <v>1.1822367492227341</v>
       </c>
-      <c r="AK14" s="19">
+      <c r="AK14" s="23">
         <f t="shared" ref="AK14" si="94">1.5*K14 / AH14</f>
         <v>0.38899188724237316</v>
       </c>
-      <c r="AM14" s="19">
+      <c r="AM14" s="23">
         <f t="shared" ref="AM14:AN14" si="95">ABS((D14*1.5) / $B$43)</f>
         <v>0.43726393755594456</v>
       </c>
-      <c r="AN14" s="19">
+      <c r="AN14" s="23">
         <f t="shared" si="95"/>
         <v>1.7264791147564267</v>
       </c>
-      <c r="AP14" s="21">
+      <c r="AP14" s="24">
         <f t="shared" ref="AP14:AQ14" si="96">1/((AJ14)+(AM14)^2)</f>
         <v>0.72810064373164252</v>
       </c>
-      <c r="AQ14" s="21">
+      <c r="AQ14" s="24">
         <f t="shared" si="96"/>
         <v>0.29676038373137631</v>
       </c>
     </row>
     <row r="15" spans="1:43">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="21"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="19"/>
-      <c r="AD15" s="19"/>
-      <c r="AE15" s="21"/>
-      <c r="AG15" s="19"/>
-      <c r="AH15" s="19"/>
-      <c r="AJ15" s="19"/>
-      <c r="AK15" s="19"/>
-      <c r="AM15" s="19"/>
-      <c r="AN15" s="19"/>
-      <c r="AP15" s="21"/>
-      <c r="AQ15" s="21"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="24"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="23"/>
+      <c r="AD15" s="23"/>
+      <c r="AE15" s="24"/>
+      <c r="AG15" s="23"/>
+      <c r="AH15" s="23"/>
+      <c r="AJ15" s="23"/>
+      <c r="AK15" s="23"/>
+      <c r="AM15" s="23"/>
+      <c r="AN15" s="23"/>
+      <c r="AP15" s="24"/>
+      <c r="AQ15" s="24"/>
     </row>
     <row r="16" spans="1:43">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="21"/>
-      <c r="Y16" s="19"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="19"/>
-      <c r="AC16" s="19"/>
-      <c r="AD16" s="19"/>
-      <c r="AE16" s="21"/>
-      <c r="AG16" s="19"/>
-      <c r="AH16" s="19"/>
-      <c r="AJ16" s="19"/>
-      <c r="AK16" s="19"/>
-      <c r="AM16" s="19"/>
-      <c r="AN16" s="19"/>
-      <c r="AP16" s="21"/>
-      <c r="AQ16" s="21"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="24"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="23"/>
+      <c r="AC16" s="23"/>
+      <c r="AD16" s="23"/>
+      <c r="AE16" s="24"/>
+      <c r="AG16" s="23"/>
+      <c r="AH16" s="23"/>
+      <c r="AJ16" s="23"/>
+      <c r="AK16" s="23"/>
+      <c r="AM16" s="23"/>
+      <c r="AN16" s="23"/>
+      <c r="AP16" s="24"/>
+      <c r="AQ16" s="24"/>
     </row>
     <row r="17" spans="1:43">
-      <c r="A17" s="19">
+      <c r="A17" s="23">
         <f>'Results_e,f'!C17</f>
         <v>6</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="23">
         <f>'Results_e,f'!E17</f>
         <v>-92.705718918306388</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="23">
         <f>'Results_e,f'!F17</f>
         <v>-30.503161720129956</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="23">
         <f>'Results_e,f'!G17</f>
         <v>39.142009467321579</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="23">
         <f>'Results_e,f'!H17</f>
         <v>154.54711478427072</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="23">
         <f>'Results_e,f'!I17</f>
         <v>23.846132839911412</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="23">
         <f>'Results_e,f'!J17</f>
         <v>7.8460788562613226</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="23">
         <f t="shared" ref="I17" si="97">MAX(-MIN(B17,0),-MIN(F17,0))</f>
         <v>92.705718918306388</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="23">
         <f t="shared" ref="J17" si="98">IF(-MIN(B17,0)&gt;=-MIN(F17,0),F17,B17)</f>
         <v>23.846132839911412</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="23">
         <f t="shared" ref="K17" si="99">MAX(-MIN(C17,0),-MIN(G17,0))</f>
         <v>30.503161720129956</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="23">
         <f t="shared" ref="L17" si="100">IF(-MIN(C17,0)&gt;=-MIN(G17,0),G17,C17)</f>
         <v>7.8460788562613226</v>
       </c>
-      <c r="N17" s="19">
+      <c r="N17" s="23">
         <f t="shared" ref="N17" si="101">IF(J17&gt;0,-J17/I17,ABS(J17)/I17)</f>
         <v>-0.25722396760576299</v>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="23">
         <f t="shared" ref="O17" si="102">IF(L17&gt;0,-L17/K17,ABS(L17)/K17)</f>
         <v>-0.25722182271628119</v>
       </c>
-      <c r="Q17" s="19">
+      <c r="Q17" s="23">
         <f t="shared" si="27"/>
         <v>-8.4494132197036098</v>
       </c>
-      <c r="R17" s="19">
+      <c r="R17" s="23">
         <f t="shared" ref="R17" si="103" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N17*$B$40^2))</f>
         <v>11.144185659158337</v>
       </c>
-      <c r="S17" s="19">
+      <c r="S17" s="23">
         <f t="shared" ref="S17" si="104" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N17*$B$40^2))</f>
         <v>5.3852033796870726</v>
       </c>
-      <c r="T17" s="19">
+      <c r="T17" s="23">
         <f t="shared" ref="T17" si="105" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N17*$B$40^2))</f>
         <v>5.0744993903524929</v>
       </c>
-      <c r="U17" s="19">
+      <c r="U17" s="23">
         <f t="shared" ref="U17" si="106" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N17*$B$40^2))</f>
         <v>5.6620909582159022</v>
       </c>
-      <c r="V17" s="19">
+      <c r="V17" s="23">
         <f t="shared" ref="V17" si="107" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$N17*$B$40^2))</f>
         <v>6.6795340633854634</v>
       </c>
-      <c r="W17" s="21">
+      <c r="W17" s="24">
         <f t="shared" ref="W17" si="108">_xlfn.MINIFS(Q17:V17,Q17:V17,"&gt;0")</f>
         <v>5.0744993903524929</v>
       </c>
-      <c r="Y17" s="19">
+      <c r="Y17" s="23">
         <f t="shared" ref="Y17" si="109" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O17*$B$40^2))</f>
         <v>-8.4495372561780275</v>
       </c>
-      <c r="Z17" s="19">
+      <c r="Z17" s="23">
         <f t="shared" ref="Z17" si="110" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O17*$B$40^2))</f>
         <v>11.144057987371763</v>
       </c>
-      <c r="AA17" s="19">
+      <c r="AA17" s="23">
         <f t="shared" ref="AA17" si="111" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O17*$B$40^2))</f>
         <v>5.3851878290604667</v>
       </c>
-      <c r="AB17" s="19">
+      <c r="AB17" s="23">
         <f t="shared" ref="AB17" si="112" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O17*$B$40^2))</f>
         <v>5.0744922322861745</v>
       </c>
-      <c r="AC17" s="19">
+      <c r="AC17" s="23">
         <f t="shared" ref="AC17" si="113" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O17*$B$40^2))</f>
         <v>5.6620861400093005</v>
       </c>
-      <c r="AD17" s="19">
+      <c r="AD17" s="23">
         <f t="shared" ref="AD17" si="114" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O17*$B$40^2))</f>
         <v>6.6795302355170527</v>
       </c>
-      <c r="AE17" s="21">
+      <c r="AE17" s="24">
         <f t="shared" ref="AE17" si="115">_xlfn.MINIFS(Y17:AD17,Y17:AD17,"&gt;0")</f>
         <v>5.0744922322861745</v>
       </c>
-      <c r="AG17" s="19">
+      <c r="AG17" s="23">
         <f t="shared" ref="AG17" si="116">W17*$B$41</f>
         <v>117.79445520116484</v>
       </c>
-      <c r="AH17" s="19">
+      <c r="AH17" s="23">
         <f t="shared" ref="AH17" si="117">AE17*$B$41</f>
         <v>117.79428904082911</v>
       </c>
-      <c r="AJ17" s="19">
+      <c r="AJ17" s="23">
         <f t="shared" ref="AJ17" si="118">1.5*I17 / AG17</f>
         <v>1.180518880451382</v>
       </c>
-      <c r="AK17" s="19">
+      <c r="AK17" s="23">
         <f t="shared" ref="AK17" si="119">1.5*K17 / AH17</f>
         <v>0.38842920953778765</v>
       </c>
-      <c r="AM17" s="19">
+      <c r="AM17" s="23">
         <f t="shared" ref="AM17:AN17" si="120">ABS((D17*1.5) / $B$43)</f>
         <v>0.43726133776514203</v>
       </c>
-      <c r="AN17" s="19">
+      <c r="AN17" s="23">
         <f t="shared" si="120"/>
         <v>1.7264693120758521</v>
       </c>
-      <c r="AP17" s="21">
+      <c r="AP17" s="24">
         <f t="shared" ref="AP17:AQ17" si="121">1/((AJ17)+(AM17)^2)</f>
         <v>0.72901368726872717</v>
       </c>
-      <c r="AQ17" s="21">
+      <c r="AQ17" s="24">
         <f t="shared" si="121"/>
         <v>0.29681292711152363</v>
       </c>
     </row>
     <row r="18" spans="1:43">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="21"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="19"/>
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="21"/>
-      <c r="AG18" s="19"/>
-      <c r="AH18" s="19"/>
-      <c r="AJ18" s="19"/>
-      <c r="AK18" s="19"/>
-      <c r="AM18" s="19"/>
-      <c r="AN18" s="19"/>
-      <c r="AP18" s="21"/>
-      <c r="AQ18" s="21"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="24"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="23"/>
+      <c r="AD18" s="23"/>
+      <c r="AE18" s="24"/>
+      <c r="AG18" s="23"/>
+      <c r="AH18" s="23"/>
+      <c r="AJ18" s="23"/>
+      <c r="AK18" s="23"/>
+      <c r="AM18" s="23"/>
+      <c r="AN18" s="23"/>
+      <c r="AP18" s="24"/>
+      <c r="AQ18" s="24"/>
     </row>
     <row r="19" spans="1:43">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="21"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
-      <c r="AE19" s="21"/>
-      <c r="AG19" s="19"/>
-      <c r="AH19" s="19"/>
-      <c r="AJ19" s="19"/>
-      <c r="AK19" s="19"/>
-      <c r="AM19" s="19"/>
-      <c r="AN19" s="19"/>
-      <c r="AP19" s="21"/>
-      <c r="AQ19" s="21"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="23"/>
+      <c r="W19" s="24"/>
+      <c r="Y19" s="23"/>
+      <c r="Z19" s="23"/>
+      <c r="AA19" s="23"/>
+      <c r="AB19" s="23"/>
+      <c r="AC19" s="23"/>
+      <c r="AD19" s="23"/>
+      <c r="AE19" s="24"/>
+      <c r="AG19" s="23"/>
+      <c r="AH19" s="23"/>
+      <c r="AJ19" s="23"/>
+      <c r="AK19" s="23"/>
+      <c r="AM19" s="23"/>
+      <c r="AN19" s="23"/>
+      <c r="AP19" s="24"/>
+      <c r="AQ19" s="24"/>
     </row>
     <row r="20" spans="1:43">
-      <c r="A20" s="19">
+      <c r="A20" s="23">
         <f>'Results_e,f'!C20</f>
         <v>7</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="23">
         <f>'Results_e,f'!E20</f>
         <v>-93.424368299081564</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="23">
         <f>'Results_e,f'!F20</f>
         <v>-30.739834806709119</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="23">
         <f>'Results_e,f'!G20</f>
         <v>39.144665401201102</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="23">
         <f>'Results_e,f'!H20</f>
         <v>154.55816907323165</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="23">
         <f>'Results_e,f'!I20</f>
         <v>23.846126383365522</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="23">
         <f>'Results_e,f'!J20</f>
         <v>7.84604327052398</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="23">
         <f t="shared" ref="I20" si="122">MAX(-MIN(B20,0),-MIN(F20,0))</f>
         <v>93.424368299081564</v>
       </c>
-      <c r="J20" s="19">
+      <c r="J20" s="23">
         <f t="shared" ref="J20" si="123">IF(-MIN(B20,0)&gt;=-MIN(F20,0),F20,B20)</f>
         <v>23.846126383365522</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="23">
         <f t="shared" ref="K20" si="124">MAX(-MIN(C20,0),-MIN(G20,0))</f>
         <v>30.739834806709119</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="23">
         <f t="shared" ref="L20" si="125">IF(-MIN(C20,0)&gt;=-MIN(G20,0),G20,C20)</f>
         <v>7.84604327052398</v>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="23">
         <f t="shared" ref="N20" si="126">IF(J20&gt;0,-J20/I20,ABS(J20)/I20)</f>
         <v>-0.25524525150682714</v>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="23">
         <f t="shared" ref="O20" si="127">IF(L20&gt;0,-L20/K20,ABS(L20)/K20)</f>
         <v>-0.25524025486342378</v>
       </c>
-      <c r="Q20" s="19">
+      <c r="Q20" s="23">
         <f t="shared" ref="Q20" si="128" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$N20*$B$40^2))</f>
         <v>-8.5654092628234917</v>
       </c>
-      <c r="R20" s="19">
+      <c r="R20" s="23">
         <f t="shared" ref="R20" si="129" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N20*$B$40^2))</f>
         <v>11.027635587083893</v>
       </c>
-      <c r="S20" s="19">
+      <c r="S20" s="23">
         <f t="shared" ref="S20" si="130" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N20*$B$40^2))</f>
         <v>5.3708955976353447</v>
       </c>
-      <c r="T20" s="19">
+      <c r="T20" s="23">
         <f t="shared" ref="T20" si="131" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N20*$B$40^2))</f>
         <v>5.067904461531942</v>
       </c>
-      <c r="U20" s="19">
+      <c r="U20" s="23">
         <f t="shared" ref="U20" si="132" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N20*$B$40^2))</f>
         <v>5.6576495207256086</v>
       </c>
-      <c r="V20" s="19">
+      <c r="V20" s="23">
         <f t="shared" ref="V20" si="133" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$N20*$B$40^2))</f>
         <v>6.6760046195440674</v>
       </c>
-      <c r="W20" s="21">
+      <c r="W20" s="24">
         <f t="shared" ref="W20" si="134">_xlfn.MINIFS(Q20:V20,Q20:V20,"&gt;0")</f>
         <v>5.067904461531942</v>
       </c>
-      <c r="Y20" s="19">
+      <c r="Y20" s="23">
         <f t="shared" ref="Y20" si="135" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O20*$B$40^2))</f>
         <v>-8.5657062069013943</v>
       </c>
-      <c r="Z20" s="19">
+      <c r="Z20" s="23">
         <f t="shared" ref="Z20" si="136" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O20*$B$40^2))</f>
         <v>11.027344361172178</v>
       </c>
-      <c r="AA20" s="19">
+      <c r="AA20" s="23">
         <f t="shared" ref="AA20" si="137" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O20*$B$40^2))</f>
         <v>5.3708595639342294</v>
       </c>
-      <c r="AB20" s="19">
+      <c r="AB20" s="23">
         <f t="shared" ref="AB20" si="138" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O20*$B$40^2))</f>
         <v>5.0678878297504486</v>
       </c>
-      <c r="AC20" s="19">
+      <c r="AC20" s="23">
         <f t="shared" ref="AC20" si="139" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O20*$B$40^2))</f>
         <v>5.6576383140510211</v>
       </c>
-      <c r="AD20" s="19">
+      <c r="AD20" s="23">
         <f t="shared" ref="AD20" si="140" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O20*$B$40^2))</f>
         <v>6.6759957117324271</v>
       </c>
-      <c r="AE20" s="21">
+      <c r="AE20" s="24">
         <f t="shared" ref="AE20" si="141">_xlfn.MINIFS(Y20:AD20,Y20:AD20,"&gt;0")</f>
         <v>5.0678878297504486</v>
       </c>
-      <c r="AG20" s="19">
+      <c r="AG20" s="23">
         <f t="shared" ref="AG20" si="142">W20*$B$41</f>
         <v>117.64136698738277</v>
       </c>
-      <c r="AH20" s="19">
+      <c r="AH20" s="23">
         <f t="shared" ref="AH20" si="143">AE20*$B$41</f>
         <v>117.64098091350841</v>
       </c>
-      <c r="AJ20" s="19">
+      <c r="AJ20" s="23">
         <f t="shared" ref="AJ20" si="144">1.5*I20 / AG20</f>
         <v>1.1912183276793462</v>
       </c>
-      <c r="AK20" s="19">
+      <c r="AK20" s="23">
         <f t="shared" ref="AK20" si="145">1.5*K20 / AH20</f>
         <v>0.39195314296099182</v>
       </c>
-      <c r="AM20" s="19">
+      <c r="AM20" s="23">
         <f t="shared" ref="AM20:AN20" si="146">ABS((D20*1.5) / $B$43)</f>
         <v>0.43729100760624062</v>
       </c>
-      <c r="AN20" s="19">
+      <c r="AN20" s="23">
         <f t="shared" si="146"/>
         <v>1.7265928012182052</v>
       </c>
-      <c r="AP20" s="21">
+      <c r="AP20" s="24">
         <f t="shared" ref="AP20:AQ20" si="147">1/((AJ20)+(AM20)^2)</f>
         <v>0.7233577818528647</v>
       </c>
-      <c r="AQ20" s="21">
+      <c r="AQ20" s="24">
         <f t="shared" si="147"/>
         <v>0.2964653171749963</v>
       </c>
     </row>
     <row r="21" spans="1:43">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="21"/>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="19"/>
-      <c r="AB21" s="19"/>
-      <c r="AC21" s="19"/>
-      <c r="AD21" s="19"/>
-      <c r="AE21" s="21"/>
-      <c r="AG21" s="19"/>
-      <c r="AH21" s="19"/>
-      <c r="AJ21" s="19"/>
-      <c r="AK21" s="19"/>
-      <c r="AM21" s="19"/>
-      <c r="AN21" s="19"/>
-      <c r="AP21" s="21"/>
-      <c r="AQ21" s="21"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="23"/>
+      <c r="V21" s="23"/>
+      <c r="W21" s="24"/>
+      <c r="Y21" s="23"/>
+      <c r="Z21" s="23"/>
+      <c r="AA21" s="23"/>
+      <c r="AB21" s="23"/>
+      <c r="AC21" s="23"/>
+      <c r="AD21" s="23"/>
+      <c r="AE21" s="24"/>
+      <c r="AG21" s="23"/>
+      <c r="AH21" s="23"/>
+      <c r="AJ21" s="23"/>
+      <c r="AK21" s="23"/>
+      <c r="AM21" s="23"/>
+      <c r="AN21" s="23"/>
+      <c r="AP21" s="24"/>
+      <c r="AQ21" s="24"/>
     </row>
     <row r="22" spans="1:43">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="21"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="19"/>
-      <c r="AE22" s="21"/>
-      <c r="AG22" s="19"/>
-      <c r="AH22" s="19"/>
-      <c r="AJ22" s="19"/>
-      <c r="AK22" s="19"/>
-      <c r="AM22" s="19"/>
-      <c r="AN22" s="19"/>
-      <c r="AP22" s="21"/>
-      <c r="AQ22" s="21"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="24"/>
+      <c r="Y22" s="23"/>
+      <c r="Z22" s="23"/>
+      <c r="AA22" s="23"/>
+      <c r="AB22" s="23"/>
+      <c r="AC22" s="23"/>
+      <c r="AD22" s="23"/>
+      <c r="AE22" s="24"/>
+      <c r="AG22" s="23"/>
+      <c r="AH22" s="23"/>
+      <c r="AJ22" s="23"/>
+      <c r="AK22" s="23"/>
+      <c r="AM22" s="23"/>
+      <c r="AN22" s="23"/>
+      <c r="AP22" s="24"/>
+      <c r="AQ22" s="24"/>
     </row>
     <row r="23" spans="1:43">
-      <c r="A23" s="19">
+      <c r="A23" s="23">
         <f>'Results_e,f'!C23</f>
         <v>8</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="23">
         <f>'Results_e,f'!E23</f>
         <v>-97.764264124313669</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="23">
         <f>'Results_e,f'!F23</f>
         <v>-32.167782985717324</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="23">
         <f>'Results_e,f'!G23</f>
         <v>39.2655607783934</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="23">
         <f>'Results_e,f'!H23</f>
         <v>155.03567954368407</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="23">
         <f>'Results_e,f'!I23</f>
         <v>23.846122984307367</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="23">
         <f>'Results_e,f'!J23</f>
         <v>7.846074605933512</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="23">
         <f t="shared" ref="I23" si="148">MAX(-MIN(B23,0),-MIN(F23,0))</f>
         <v>97.764264124313669</v>
       </c>
-      <c r="J23" s="19">
+      <c r="J23" s="23">
         <f t="shared" ref="J23" si="149">IF(-MIN(B23,0)&gt;=-MIN(F23,0),F23,B23)</f>
         <v>23.846122984307367</v>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="23">
         <f t="shared" ref="K23" si="150">MAX(-MIN(C23,0),-MIN(G23,0))</f>
         <v>32.167782985717324</v>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="23">
         <f t="shared" ref="L23" si="151">IF(-MIN(C23,0)&gt;=-MIN(G23,0),G23,C23)</f>
         <v>7.846074605933512</v>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="23">
         <f t="shared" ref="N23" si="152">IF(J23&gt;0,-J23/I23,ABS(J23)/I23)</f>
         <v>-0.24391451414174672</v>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="23">
         <f t="shared" ref="O23" si="153">IF(L23&gt;0,-L23/K23,ABS(L23)/K23)</f>
         <v>-0.24391095306186358</v>
       </c>
-      <c r="Q23" s="19">
+      <c r="Q23" s="23">
         <f t="shared" ref="Q23" si="154" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$N23*$B$40^2))</f>
         <v>-9.2962068219725733</v>
       </c>
-      <c r="R23" s="19">
+      <c r="R23" s="23">
         <f t="shared" ref="R23" si="155" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N23*$B$40^2))</f>
         <v>10.404530385748362</v>
       </c>
-      <c r="S23" s="19">
+      <c r="S23" s="23">
         <f t="shared" ref="S23" si="156" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N23*$B$40^2))</f>
         <v>5.290407070120505</v>
       </c>
-      <c r="T23" s="19">
+      <c r="T23" s="23">
         <f t="shared" ref="T23" si="157" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N23*$B$40^2))</f>
         <v>5.0304675557748952</v>
       </c>
-      <c r="U23" s="19">
+      <c r="U23" s="23">
         <f t="shared" ref="U23" si="158" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N23*$B$40^2))</f>
         <v>5.6323500731417546</v>
       </c>
-      <c r="V23" s="19">
+      <c r="V23" s="23">
         <f t="shared" ref="V23" si="159" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$N23*$B$40^2))</f>
         <v>6.6558655531471693</v>
       </c>
-      <c r="W23" s="21">
+      <c r="W23" s="24">
         <f t="shared" ref="W23" si="160">_xlfn.MINIFS(Q23:V23,Q23:V23,"&gt;0")</f>
         <v>5.0304675557748952</v>
       </c>
-      <c r="Y23" s="19">
+      <c r="Y23" s="23">
         <f t="shared" ref="Y23" si="161" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O23*$B$40^2))</f>
         <v>-9.2964561034070776</v>
       </c>
-      <c r="Z23" s="19">
+      <c r="Z23" s="23">
         <f t="shared" ref="Z23" si="162" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O23*$B$40^2))</f>
         <v>10.404345621779038</v>
       </c>
-      <c r="AA23" s="19">
+      <c r="AA23" s="23">
         <f t="shared" ref="AA23" si="163" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O23*$B$40^2))</f>
         <v>5.2903821529996078</v>
       </c>
-      <c r="AB23" s="19">
+      <c r="AB23" s="23">
         <f t="shared" ref="AB23" si="164" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O23*$B$40^2))</f>
         <v>5.0304558768621455</v>
       </c>
-      <c r="AC23" s="19">
+      <c r="AC23" s="23">
         <f t="shared" ref="AC23" si="165" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O23*$B$40^2))</f>
         <v>5.6323421574737553</v>
       </c>
-      <c r="AD23" s="19">
+      <c r="AD23" s="23">
         <f t="shared" ref="AD23" si="166" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O23*$B$40^2))</f>
         <v>6.6558592428417889</v>
       </c>
-      <c r="AE23" s="21">
+      <c r="AE23" s="24">
         <f t="shared" ref="AE23" si="167">_xlfn.MINIFS(Y23:AD23,Y23:AD23,"&gt;0")</f>
         <v>5.0304558768621455</v>
       </c>
-      <c r="AG23" s="19">
+      <c r="AG23" s="23">
         <f t="shared" ref="AG23" si="168">W23*$B$41</f>
         <v>116.77234335000632</v>
       </c>
-      <c r="AH23" s="19">
+      <c r="AH23" s="23">
         <f t="shared" ref="AH23" si="169">AE23*$B$41</f>
         <v>116.77207224717255</v>
       </c>
-      <c r="AJ23" s="19">
+      <c r="AJ23" s="23">
         <f t="shared" ref="AJ23" si="170">1.5*I23 / AG23</f>
         <v>1.2558315777471512</v>
       </c>
-      <c r="AK23" s="19">
+      <c r="AK23" s="23">
         <f t="shared" ref="AK23" si="171">1.5*K23 / AH23</f>
         <v>0.41321245354318292</v>
       </c>
-      <c r="AM23" s="19">
+      <c r="AM23" s="23">
         <f t="shared" ref="AM23:AN23" si="172">ABS((D23*1.5) / $B$43)</f>
         <v>0.43864154824225116</v>
       </c>
-      <c r="AN23" s="19">
+      <c r="AN23" s="23">
         <f t="shared" si="172"/>
         <v>1.7319271432703476</v>
       </c>
-      <c r="AP23" s="21">
+      <c r="AP23" s="24">
         <f t="shared" ref="AP23:AQ23" si="173">1/((AJ23)+(AM23)^2)</f>
         <v>0.69049424883822907</v>
       </c>
-      <c r="AQ23" s="21">
+      <c r="AQ23" s="24">
         <f t="shared" si="173"/>
         <v>0.29301590010933171</v>
       </c>
     </row>
     <row r="24" spans="1:43">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="21"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="19"/>
-      <c r="AE24" s="21"/>
-      <c r="AG24" s="19"/>
-      <c r="AH24" s="19"/>
-      <c r="AJ24" s="19"/>
-      <c r="AK24" s="19"/>
-      <c r="AM24" s="19"/>
-      <c r="AN24" s="19"/>
-      <c r="AP24" s="21"/>
-      <c r="AQ24" s="21"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
+      <c r="W24" s="24"/>
+      <c r="Y24" s="23"/>
+      <c r="Z24" s="23"/>
+      <c r="AA24" s="23"/>
+      <c r="AB24" s="23"/>
+      <c r="AC24" s="23"/>
+      <c r="AD24" s="23"/>
+      <c r="AE24" s="24"/>
+      <c r="AG24" s="23"/>
+      <c r="AH24" s="23"/>
+      <c r="AJ24" s="23"/>
+      <c r="AK24" s="23"/>
+      <c r="AM24" s="23"/>
+      <c r="AN24" s="23"/>
+      <c r="AP24" s="24"/>
+      <c r="AQ24" s="24"/>
     </row>
     <row r="25" spans="1:43">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="21"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="19"/>
-      <c r="AE25" s="21"/>
-      <c r="AG25" s="19"/>
-      <c r="AH25" s="19"/>
-      <c r="AJ25" s="19"/>
-      <c r="AK25" s="19"/>
-      <c r="AM25" s="19"/>
-      <c r="AN25" s="19"/>
-      <c r="AP25" s="21"/>
-      <c r="AQ25" s="21"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="23"/>
+      <c r="V25" s="23"/>
+      <c r="W25" s="24"/>
+      <c r="Y25" s="23"/>
+      <c r="Z25" s="23"/>
+      <c r="AA25" s="23"/>
+      <c r="AB25" s="23"/>
+      <c r="AC25" s="23"/>
+      <c r="AD25" s="23"/>
+      <c r="AE25" s="24"/>
+      <c r="AG25" s="23"/>
+      <c r="AH25" s="23"/>
+      <c r="AJ25" s="23"/>
+      <c r="AK25" s="23"/>
+      <c r="AM25" s="23"/>
+      <c r="AN25" s="23"/>
+      <c r="AP25" s="24"/>
+      <c r="AQ25" s="24"/>
     </row>
     <row r="26" spans="1:43">
-      <c r="A26" s="19">
+      <c r="A26" s="23">
         <f>'Results_e,f'!C26</f>
         <v>9</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="23">
         <f>'Results_e,f'!E26</f>
         <v>-99.814182963562089</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="23">
         <f>'Results_e,f'!F26</f>
         <v>-32.842064124437279</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="23">
         <f>'Results_e,f'!G26</f>
         <v>39.284209508678494</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="23">
         <f>'Results_e,f'!H26</f>
         <v>155.109244290373</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="23">
         <f>'Results_e,f'!I26</f>
         <v>23.846115288967287</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="23">
         <f>'Results_e,f'!J26</f>
         <v>7.8460258897336743</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="23">
         <f t="shared" ref="I26" si="174">MAX(-MIN(B26,0),-MIN(F26,0))</f>
         <v>99.814182963562089</v>
       </c>
-      <c r="J26" s="19">
+      <c r="J26" s="23">
         <f t="shared" ref="J26" si="175">IF(-MIN(B26,0)&gt;=-MIN(F26,0),F26,B26)</f>
         <v>23.846115288967287</v>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="23">
         <f t="shared" ref="K26" si="176">MAX(-MIN(C26,0),-MIN(G26,0))</f>
         <v>32.842064124437279</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="23">
         <f t="shared" ref="L26" si="177">IF(-MIN(C26,0)&gt;=-MIN(G26,0),G26,C26)</f>
         <v>7.8460258897336743</v>
       </c>
-      <c r="N26" s="19">
+      <c r="N26" s="23">
         <f t="shared" ref="N26" si="178">IF(J26&gt;0,-J26/I26,ABS(J26)/I26)</f>
         <v>-0.23890507922779358</v>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="23">
         <f t="shared" ref="O26" si="179">IF(L26&gt;0,-L26/K26,ABS(L26)/K26)</f>
         <v>-0.23890172858823347</v>
       </c>
-      <c r="Q26" s="19">
+      <c r="Q26" s="23">
         <f t="shared" ref="Q26" si="180" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$N26*$B$40^2))</f>
         <v>-9.6606116816667278</v>
       </c>
-      <c r="R26" s="19">
+      <c r="R26" s="23">
         <f t="shared" ref="R26" si="181" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N26*$B$40^2))</f>
         <v>10.150949677630891</v>
       </c>
-      <c r="S26" s="19">
+      <c r="S26" s="23">
         <f t="shared" ref="S26" si="182" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N26*$B$40^2))</f>
         <v>5.2555862492704621</v>
       </c>
-      <c r="T26" s="19">
+      <c r="T26" s="23">
         <f t="shared" ref="T26" si="183" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N26*$B$40^2))</f>
         <v>5.0140920623171503</v>
       </c>
-      <c r="U26" s="19">
+      <c r="U26" s="23">
         <f t="shared" ref="U26" si="184" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N26*$B$40^2))</f>
         <v>5.6212369160621911</v>
       </c>
-      <c r="V26" s="19">
+      <c r="V26" s="23">
         <f t="shared" ref="V26" si="185" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$N26*$B$40^2))</f>
         <v>6.6470005481454706</v>
       </c>
-      <c r="W26" s="21">
+      <c r="W26" s="24">
         <f t="shared" ref="W26" si="186">_xlfn.MINIFS(Q26:V26,Q26:V26,"&gt;0")</f>
         <v>5.0140920623171503</v>
       </c>
-      <c r="Y26" s="19">
+      <c r="Y26" s="23">
         <f t="shared" ref="Y26" si="187" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O26*$B$40^2))</f>
         <v>-9.6608649806045896</v>
       </c>
-      <c r="Z26" s="19">
+      <c r="Z26" s="23">
         <f t="shared" ref="Z26" si="188" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O26*$B$40^2))</f>
         <v>10.150784202666618</v>
       </c>
-      <c r="AA26" s="19">
+      <c r="AA26" s="23">
         <f t="shared" ref="AA26" si="189" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O26*$B$40^2))</f>
         <v>5.2555631122120037</v>
       </c>
-      <c r="AB26" s="19">
+      <c r="AB26" s="23">
         <f t="shared" ref="AB26" si="190" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O26*$B$40^2))</f>
         <v>5.014081144988733</v>
       </c>
-      <c r="AC26" s="19">
+      <c r="AC26" s="23">
         <f t="shared" ref="AC26" si="191" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O26*$B$40^2))</f>
         <v>5.6212294975279953</v>
       </c>
-      <c r="AD26" s="19">
+      <c r="AD26" s="23">
         <f t="shared" ref="AD26" si="192" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O26*$B$40^2))</f>
         <v>6.6469946265498656</v>
       </c>
-      <c r="AE26" s="21">
+      <c r="AE26" s="24">
         <f t="shared" ref="AE26" si="193">_xlfn.MINIFS(Y26:AD26,Y26:AD26,"&gt;0")</f>
         <v>5.014081144988733</v>
       </c>
-      <c r="AG26" s="19">
+      <c r="AG26" s="23">
         <f t="shared" ref="AG26" si="194">W26*$B$41</f>
         <v>116.39221869491767</v>
       </c>
-      <c r="AH26" s="19">
+      <c r="AH26" s="23">
         <f t="shared" ref="AH26" si="195">AE26*$B$41</f>
         <v>116.39196527075615</v>
       </c>
-      <c r="AJ26" s="19">
+      <c r="AJ26" s="23">
         <f t="shared" ref="AJ26" si="196">1.5*I26 / AG26</f>
         <v>1.2863512365700853</v>
       </c>
-      <c r="AK26" s="19">
+      <c r="AK26" s="23">
         <f t="shared" ref="AK26" si="197">1.5*K26 / AH26</f>
         <v>0.42325169157559905</v>
       </c>
-      <c r="AM26" s="19">
+      <c r="AM26" s="23">
         <f t="shared" ref="AM26:AN26" si="198">ABS((D26*1.5) / $B$43)</f>
         <v>0.43884987604307318</v>
       </c>
-      <c r="AN26" s="19">
+      <c r="AN26" s="23">
         <f t="shared" si="198"/>
         <v>1.7327489462382408</v>
       </c>
-      <c r="AP26" s="21">
+      <c r="AP26" s="24">
         <f t="shared" ref="AP26:AQ26" si="199">1/((AJ26)+(AM26)^2)</f>
         <v>0.6761597465370135</v>
       </c>
-      <c r="AQ26" s="21">
+      <c r="AQ26" s="24">
         <f t="shared" si="199"/>
         <v>0.29191364731294317</v>
       </c>
     </row>
     <row r="27" spans="1:43">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="19"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="21"/>
-      <c r="Y27" s="19"/>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="19"/>
-      <c r="AB27" s="19"/>
-      <c r="AC27" s="19"/>
-      <c r="AD27" s="19"/>
-      <c r="AE27" s="21"/>
-      <c r="AG27" s="19"/>
-      <c r="AH27" s="19"/>
-      <c r="AJ27" s="19"/>
-      <c r="AK27" s="19"/>
-      <c r="AM27" s="19"/>
-      <c r="AN27" s="19"/>
-      <c r="AP27" s="21"/>
-      <c r="AQ27" s="21"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="24"/>
+      <c r="Y27" s="23"/>
+      <c r="Z27" s="23"/>
+      <c r="AA27" s="23"/>
+      <c r="AB27" s="23"/>
+      <c r="AC27" s="23"/>
+      <c r="AD27" s="23"/>
+      <c r="AE27" s="24"/>
+      <c r="AG27" s="23"/>
+      <c r="AH27" s="23"/>
+      <c r="AJ27" s="23"/>
+      <c r="AK27" s="23"/>
+      <c r="AM27" s="23"/>
+      <c r="AN27" s="23"/>
+      <c r="AP27" s="24"/>
+      <c r="AQ27" s="24"/>
     </row>
     <row r="28" spans="1:43">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="21"/>
-      <c r="Y28" s="19"/>
-      <c r="Z28" s="19"/>
-      <c r="AA28" s="19"/>
-      <c r="AB28" s="19"/>
-      <c r="AC28" s="19"/>
-      <c r="AD28" s="19"/>
-      <c r="AE28" s="21"/>
-      <c r="AG28" s="19"/>
-      <c r="AH28" s="19"/>
-      <c r="AJ28" s="19"/>
-      <c r="AK28" s="19"/>
-      <c r="AM28" s="19"/>
-      <c r="AN28" s="19"/>
-      <c r="AP28" s="21"/>
-      <c r="AQ28" s="21"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="24"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="23"/>
+      <c r="AA28" s="23"/>
+      <c r="AB28" s="23"/>
+      <c r="AC28" s="23"/>
+      <c r="AD28" s="23"/>
+      <c r="AE28" s="24"/>
+      <c r="AG28" s="23"/>
+      <c r="AH28" s="23"/>
+      <c r="AJ28" s="23"/>
+      <c r="AK28" s="23"/>
+      <c r="AM28" s="23"/>
+      <c r="AN28" s="23"/>
+      <c r="AP28" s="24"/>
+      <c r="AQ28" s="24"/>
     </row>
     <row r="29" spans="1:43">
-      <c r="A29" s="19">
+      <c r="A29" s="23">
         <f>'Results_e,f'!C29</f>
         <v>10</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="23">
         <f>'Results_e,f'!E29</f>
         <v>-74.593693830984463</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="23">
         <f>'Results_e,f'!F29</f>
         <v>-24.543661857522295</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="23">
         <f>'Results_e,f'!G29</f>
         <v>39.523201047199258</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="23">
         <f>'Results_e,f'!H29</f>
         <v>156.05293772728351</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="23">
         <f>'Results_e,f'!I29</f>
         <v>23.846151722228072</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="23">
         <f>'Results_e,f'!J29</f>
         <v>7.8461967836059543</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="23">
         <f t="shared" ref="I29" si="200">MAX(-MIN(B29,0),-MIN(F29,0))</f>
         <v>74.593693830984463</v>
       </c>
-      <c r="J29" s="19">
+      <c r="J29" s="23">
         <f t="shared" ref="J29" si="201">IF(-MIN(B29,0)&gt;=-MIN(F29,0),F29,B29)</f>
         <v>23.846151722228072</v>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="23">
         <f t="shared" ref="K29" si="202">MAX(-MIN(C29,0),-MIN(G29,0))</f>
         <v>24.543661857522295</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="23">
         <f t="shared" ref="L29" si="203">IF(-MIN(C29,0)&gt;=-MIN(G29,0),G29,C29)</f>
         <v>7.8461967836059543</v>
       </c>
-      <c r="N29" s="19">
+      <c r="N29" s="23">
         <f t="shared" ref="N29" si="204">IF(J29&gt;0,-J29/I29,ABS(J29)/I29)</f>
         <v>-0.31968053192618467</v>
       </c>
-      <c r="O29" s="19">
+      <c r="O29" s="23">
         <f t="shared" ref="O29" si="205">IF(L29&gt;0,-L29/K29,ABS(L29)/K29)</f>
         <v>-0.31968321716432069</v>
       </c>
-      <c r="Q29" s="19">
+      <c r="Q29" s="23">
         <f t="shared" ref="Q29" si="206" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$N29*$B$40^2))</f>
         <v>-5.919218150052723</v>
       </c>
-      <c r="R29" s="19">
+      <c r="R29" s="23">
         <f t="shared" ref="R29" si="207" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N29*$B$40^2))</f>
         <v>16.722942644020264</v>
       </c>
-      <c r="S29" s="19">
+      <c r="S29" s="23">
         <f t="shared" ref="S29" si="208" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N29*$B$40^2))</f>
         <v>5.8795906742536372</v>
       </c>
-      <c r="T29" s="19">
+      <c r="T29" s="23">
         <f t="shared" ref="T29" si="209" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N29*$B$40^2))</f>
         <v>5.291861982915643</v>
       </c>
-      <c r="U29" s="19">
+      <c r="U29" s="23">
         <f t="shared" ref="U29" si="210" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N29*$B$40^2))</f>
         <v>5.8059561973624421</v>
       </c>
-      <c r="V29" s="19">
+      <c r="V29" s="23">
         <f t="shared" ref="V29" si="211" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$N29*$B$40^2))</f>
         <v>6.7928885567872612</v>
       </c>
-      <c r="W29" s="21">
+      <c r="W29" s="24">
         <f t="shared" ref="W29" si="212">_xlfn.MINIFS(Q29:V29,Q29:V29,"&gt;0")</f>
         <v>5.291861982915643</v>
       </c>
-      <c r="Y29" s="19">
+      <c r="Y29" s="23">
         <f t="shared" ref="Y29" si="213" xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O29*$B$40^2))</f>
         <v>-5.9191419437439672</v>
       </c>
-      <c r="Z29" s="19">
+      <c r="Z29" s="23">
         <f t="shared" ref="Z29" si="214" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$O29*$B$40^2))</f>
         <v>16.723302572215211</v>
       </c>
-      <c r="AA29" s="19">
+      <c r="AA29" s="23">
         <f t="shared" ref="AA29" si="215" xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$O29*$B$40^2))</f>
         <v>5.8796138812382379</v>
       </c>
-      <c r="AB29" s="19">
+      <c r="AB29" s="23">
         <f t="shared" ref="AB29" si="216" xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$O29*$B$40^2))</f>
         <v>5.2918717284492942</v>
       </c>
-      <c r="AC29" s="19">
+      <c r="AC29" s="23">
         <f t="shared" ref="AC29" si="217" xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$O29*$B$40^2))</f>
         <v>5.805962539825928</v>
       </c>
-      <c r="AD29" s="19">
+      <c r="AD29" s="23">
         <f t="shared" ref="AD29" si="218" xml:space="preserve"> ((K$35^2+$B$40^2)^2)/($B$40^2*(K$35^2+$O29*$B$40^2))</f>
         <v>6.7928935130245858</v>
       </c>
-      <c r="AE29" s="21">
+      <c r="AE29" s="24">
         <f t="shared" ref="AE29" si="219">_xlfn.MINIFS(Y29:AD29,Y29:AD29,"&gt;0")</f>
         <v>5.2918717284492942</v>
       </c>
-      <c r="AG29" s="19">
+      <c r="AG29" s="23">
         <f t="shared" ref="AG29" si="220">W29*$B$41</f>
         <v>122.84009738229641</v>
       </c>
-      <c r="AH29" s="19">
+      <c r="AH29" s="23">
         <f t="shared" ref="AH29" si="221">AE29*$B$41</f>
         <v>122.84032360556274</v>
       </c>
-      <c r="AJ29" s="19">
+      <c r="AJ29" s="23">
         <f t="shared" ref="AJ29" si="222">1.5*I29 / AG29</f>
         <v>0.91086333478112536</v>
       </c>
-      <c r="AK29" s="19">
+      <c r="AK29" s="23">
         <f t="shared" ref="AK29" si="223">1.5*K29 / AH29</f>
         <v>0.2997020172667168</v>
       </c>
-      <c r="AM29" s="19">
+      <c r="AM29" s="23">
         <f t="shared" ref="AM29:AN29" si="224">ABS((D29*1.5) / $B$43)</f>
         <v>0.44151968684916848</v>
       </c>
-      <c r="AN29" s="19">
+      <c r="AN29" s="23">
         <f t="shared" si="224"/>
         <v>1.7432910890735027</v>
       </c>
-      <c r="AP29" s="21">
+      <c r="AP29" s="24">
         <f t="shared" ref="AP29:AQ29" si="225">1/((AJ29)+(AM29)^2)</f>
         <v>0.90432023456668986</v>
       </c>
-      <c r="AQ29" s="21">
+      <c r="AQ29" s="24">
         <f t="shared" si="225"/>
         <v>0.29951187006463853</v>
       </c>
     </row>
     <row r="30" spans="1:43">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="21"/>
-      <c r="Y30" s="19"/>
-      <c r="Z30" s="19"/>
-      <c r="AA30" s="19"/>
-      <c r="AB30" s="19"/>
-      <c r="AC30" s="19"/>
-      <c r="AD30" s="19"/>
-      <c r="AE30" s="21"/>
-      <c r="AG30" s="19"/>
-      <c r="AH30" s="19"/>
-      <c r="AJ30" s="19"/>
-      <c r="AK30" s="19"/>
-      <c r="AM30" s="19"/>
-      <c r="AN30" s="19"/>
-      <c r="AP30" s="21"/>
-      <c r="AQ30" s="21"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="24"/>
+      <c r="Y30" s="23"/>
+      <c r="Z30" s="23"/>
+      <c r="AA30" s="23"/>
+      <c r="AB30" s="23"/>
+      <c r="AC30" s="23"/>
+      <c r="AD30" s="23"/>
+      <c r="AE30" s="24"/>
+      <c r="AG30" s="23"/>
+      <c r="AH30" s="23"/>
+      <c r="AJ30" s="23"/>
+      <c r="AK30" s="23"/>
+      <c r="AM30" s="23"/>
+      <c r="AN30" s="23"/>
+      <c r="AP30" s="24"/>
+      <c r="AQ30" s="24"/>
     </row>
     <row r="31" spans="1:43">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="21"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="19"/>
-      <c r="AB31" s="19"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="19"/>
-      <c r="AE31" s="21"/>
-      <c r="AG31" s="19"/>
-      <c r="AH31" s="19"/>
-      <c r="AJ31" s="19"/>
-      <c r="AK31" s="19"/>
-      <c r="AM31" s="19"/>
-      <c r="AN31" s="19"/>
-      <c r="AP31" s="21"/>
-      <c r="AQ31" s="21"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="24"/>
+      <c r="Y31" s="23"/>
+      <c r="Z31" s="23"/>
+      <c r="AA31" s="23"/>
+      <c r="AB31" s="23"/>
+      <c r="AC31" s="23"/>
+      <c r="AD31" s="23"/>
+      <c r="AE31" s="24"/>
+      <c r="AG31" s="23"/>
+      <c r="AH31" s="23"/>
+      <c r="AJ31" s="23"/>
+      <c r="AK31" s="23"/>
+      <c r="AM31" s="23"/>
+      <c r="AN31" s="23"/>
+      <c r="AP31" s="24"/>
+      <c r="AQ31" s="24"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
@@ -10627,196 +10611,144 @@
     </row>
   </sheetData>
   <mergeCells count="352">
-    <mergeCell ref="O29:O31"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="N23:N25"/>
-    <mergeCell ref="N26:N28"/>
-    <mergeCell ref="N29:N31"/>
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="O5:O7"/>
-    <mergeCell ref="O8:O10"/>
-    <mergeCell ref="O11:O13"/>
-    <mergeCell ref="O14:O16"/>
-    <mergeCell ref="O17:O19"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="N11:N13"/>
-    <mergeCell ref="N14:N16"/>
-    <mergeCell ref="N17:N19"/>
-    <mergeCell ref="O20:O22"/>
-    <mergeCell ref="O23:O25"/>
-    <mergeCell ref="O26:O28"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="K23:K25"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="K29:K31"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="L8:L10"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="L17:L19"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="K5:K7"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="K14:K16"/>
-    <mergeCell ref="K17:K19"/>
-    <mergeCell ref="L20:L22"/>
-    <mergeCell ref="L23:L25"/>
-    <mergeCell ref="L26:L28"/>
-    <mergeCell ref="L29:L31"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="J23:J25"/>
-    <mergeCell ref="J26:J28"/>
-    <mergeCell ref="J29:J31"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="I26:I28"/>
-    <mergeCell ref="I29:I31"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="T2:T4"/>
-    <mergeCell ref="U2:U4"/>
-    <mergeCell ref="V2:V4"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="U5:U7"/>
-    <mergeCell ref="V5:V7"/>
-    <mergeCell ref="U8:U10"/>
-    <mergeCell ref="V8:V10"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V13"/>
-    <mergeCell ref="Q20:Q22"/>
-    <mergeCell ref="Q23:Q25"/>
-    <mergeCell ref="Q26:Q28"/>
-    <mergeCell ref="Q29:Q31"/>
-    <mergeCell ref="R5:R7"/>
-    <mergeCell ref="S5:S7"/>
-    <mergeCell ref="T5:T7"/>
-    <mergeCell ref="R8:R10"/>
-    <mergeCell ref="S8:S10"/>
-    <mergeCell ref="T8:T10"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="R14:R16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="T14:T16"/>
-    <mergeCell ref="R23:R25"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="T23:T25"/>
-    <mergeCell ref="R29:R31"/>
-    <mergeCell ref="S29:S31"/>
-    <mergeCell ref="T29:T31"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="V29:V31"/>
-    <mergeCell ref="U14:U16"/>
-    <mergeCell ref="V14:V16"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="T17:T19"/>
-    <mergeCell ref="U17:U19"/>
-    <mergeCell ref="V17:V19"/>
-    <mergeCell ref="R20:R22"/>
-    <mergeCell ref="S20:S22"/>
-    <mergeCell ref="T20:T22"/>
-    <mergeCell ref="U20:U22"/>
-    <mergeCell ref="V20:V22"/>
-    <mergeCell ref="W23:W25"/>
-    <mergeCell ref="W26:W28"/>
-    <mergeCell ref="U23:U25"/>
-    <mergeCell ref="V23:V25"/>
-    <mergeCell ref="R26:R28"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="T26:T28"/>
-    <mergeCell ref="U26:U28"/>
-    <mergeCell ref="V26:V28"/>
+    <mergeCell ref="AQ29:AQ31"/>
+    <mergeCell ref="AQ2:AQ4"/>
+    <mergeCell ref="AQ5:AQ7"/>
+    <mergeCell ref="AQ8:AQ10"/>
+    <mergeCell ref="AQ11:AQ13"/>
+    <mergeCell ref="AQ14:AQ16"/>
+    <mergeCell ref="AQ17:AQ19"/>
+    <mergeCell ref="AQ20:AQ22"/>
+    <mergeCell ref="AQ23:AQ25"/>
+    <mergeCell ref="AQ26:AQ28"/>
+    <mergeCell ref="AN29:AN31"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="AP5:AP7"/>
+    <mergeCell ref="AP8:AP10"/>
+    <mergeCell ref="AP11:AP13"/>
+    <mergeCell ref="AP14:AP16"/>
+    <mergeCell ref="AP17:AP19"/>
+    <mergeCell ref="AP20:AP22"/>
+    <mergeCell ref="AP23:AP25"/>
+    <mergeCell ref="AP26:AP28"/>
+    <mergeCell ref="AP29:AP31"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AN5:AN7"/>
+    <mergeCell ref="AN8:AN10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AN17:AN19"/>
+    <mergeCell ref="AN20:AN22"/>
+    <mergeCell ref="AN23:AN25"/>
+    <mergeCell ref="AN26:AN28"/>
+    <mergeCell ref="AK29:AK31"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AM5:AM7"/>
+    <mergeCell ref="AM8:AM10"/>
+    <mergeCell ref="AM11:AM13"/>
+    <mergeCell ref="AM14:AM16"/>
+    <mergeCell ref="AM17:AM19"/>
+    <mergeCell ref="AM20:AM22"/>
+    <mergeCell ref="AM23:AM25"/>
+    <mergeCell ref="AM26:AM28"/>
+    <mergeCell ref="AM29:AM31"/>
+    <mergeCell ref="AK2:AK4"/>
+    <mergeCell ref="AK5:AK7"/>
+    <mergeCell ref="AK8:AK10"/>
+    <mergeCell ref="AK11:AK13"/>
+    <mergeCell ref="AK14:AK16"/>
+    <mergeCell ref="AK17:AK19"/>
+    <mergeCell ref="AK20:AK22"/>
+    <mergeCell ref="AK23:AK25"/>
+    <mergeCell ref="AK26:AK28"/>
+    <mergeCell ref="AH23:AH25"/>
+    <mergeCell ref="AH26:AH28"/>
+    <mergeCell ref="AH29:AH31"/>
+    <mergeCell ref="AJ2:AJ4"/>
+    <mergeCell ref="AJ5:AJ7"/>
+    <mergeCell ref="AJ8:AJ10"/>
+    <mergeCell ref="AJ11:AJ13"/>
+    <mergeCell ref="AJ14:AJ16"/>
+    <mergeCell ref="AJ17:AJ19"/>
+    <mergeCell ref="AJ20:AJ22"/>
+    <mergeCell ref="AJ23:AJ25"/>
+    <mergeCell ref="AJ26:AJ28"/>
+    <mergeCell ref="AJ29:AJ31"/>
+    <mergeCell ref="Y1:AD1"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="AH2:AH4"/>
+    <mergeCell ref="AH5:AH7"/>
+    <mergeCell ref="AH8:AH10"/>
+    <mergeCell ref="AH11:AH13"/>
+    <mergeCell ref="AH14:AH16"/>
+    <mergeCell ref="AH17:AH19"/>
+    <mergeCell ref="AH20:AH22"/>
+    <mergeCell ref="Y20:Y22"/>
+    <mergeCell ref="Z20:Z22"/>
+    <mergeCell ref="AA20:AA22"/>
+    <mergeCell ref="AB20:AB22"/>
+    <mergeCell ref="AC20:AC22"/>
+    <mergeCell ref="AD20:AD22"/>
+    <mergeCell ref="W2:W4"/>
+    <mergeCell ref="W5:W7"/>
+    <mergeCell ref="W8:W10"/>
+    <mergeCell ref="W11:W13"/>
+    <mergeCell ref="W14:W16"/>
+    <mergeCell ref="W17:W19"/>
+    <mergeCell ref="W20:W22"/>
+    <mergeCell ref="Q14:Q16"/>
+    <mergeCell ref="Q17:Q19"/>
+    <mergeCell ref="AE26:AE28"/>
+    <mergeCell ref="AE29:AE31"/>
+    <mergeCell ref="AG2:AG4"/>
+    <mergeCell ref="AG5:AG7"/>
+    <mergeCell ref="AG8:AG10"/>
+    <mergeCell ref="AG11:AG13"/>
+    <mergeCell ref="AG14:AG16"/>
+    <mergeCell ref="AG17:AG19"/>
+    <mergeCell ref="AG20:AG22"/>
+    <mergeCell ref="AG23:AG25"/>
+    <mergeCell ref="AG26:AG28"/>
+    <mergeCell ref="AG29:AG31"/>
+    <mergeCell ref="AE2:AE4"/>
+    <mergeCell ref="AE5:AE7"/>
+    <mergeCell ref="AE8:AE10"/>
+    <mergeCell ref="AE11:AE13"/>
+    <mergeCell ref="AE14:AE16"/>
+    <mergeCell ref="AE17:AE19"/>
+    <mergeCell ref="AE20:AE22"/>
+    <mergeCell ref="AE23:AE25"/>
+    <mergeCell ref="Y26:Y28"/>
+    <mergeCell ref="Z26:Z28"/>
+    <mergeCell ref="AA26:AA28"/>
+    <mergeCell ref="AB26:AB28"/>
+    <mergeCell ref="AC26:AC28"/>
+    <mergeCell ref="AD26:AD28"/>
+    <mergeCell ref="Y29:Y31"/>
+    <mergeCell ref="Z29:Z31"/>
+    <mergeCell ref="AA29:AA31"/>
+    <mergeCell ref="AB29:AB31"/>
+    <mergeCell ref="AC29:AC31"/>
+    <mergeCell ref="AD29:AD31"/>
+    <mergeCell ref="Y23:Y25"/>
+    <mergeCell ref="Z23:Z25"/>
+    <mergeCell ref="AA23:AA25"/>
+    <mergeCell ref="AB23:AB25"/>
+    <mergeCell ref="AC23:AC25"/>
+    <mergeCell ref="AD23:AD25"/>
+    <mergeCell ref="AD11:AD13"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="Z14:Z16"/>
+    <mergeCell ref="AA14:AA16"/>
+    <mergeCell ref="AB14:AB16"/>
+    <mergeCell ref="AC14:AC16"/>
+    <mergeCell ref="AD14:AD16"/>
+    <mergeCell ref="Y17:Y19"/>
+    <mergeCell ref="Z17:Z19"/>
+    <mergeCell ref="AA17:AA19"/>
+    <mergeCell ref="AB17:AB19"/>
+    <mergeCell ref="AC17:AC19"/>
+    <mergeCell ref="AD17:AD19"/>
     <mergeCell ref="W29:W31"/>
     <mergeCell ref="Y2:Y4"/>
     <mergeCell ref="Z2:Z4"/>
@@ -10841,144 +10773,196 @@
     <mergeCell ref="AA11:AA13"/>
     <mergeCell ref="AB11:AB13"/>
     <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="Y23:Y25"/>
-    <mergeCell ref="Z23:Z25"/>
-    <mergeCell ref="AA23:AA25"/>
-    <mergeCell ref="AB23:AB25"/>
-    <mergeCell ref="AC23:AC25"/>
-    <mergeCell ref="AD23:AD25"/>
-    <mergeCell ref="AD11:AD13"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="Z14:Z16"/>
-    <mergeCell ref="AA14:AA16"/>
-    <mergeCell ref="AB14:AB16"/>
-    <mergeCell ref="AC14:AC16"/>
-    <mergeCell ref="AD14:AD16"/>
-    <mergeCell ref="Y17:Y19"/>
-    <mergeCell ref="Z17:Z19"/>
-    <mergeCell ref="AA17:AA19"/>
-    <mergeCell ref="AB17:AB19"/>
-    <mergeCell ref="AC17:AC19"/>
-    <mergeCell ref="AD17:AD19"/>
-    <mergeCell ref="Y26:Y28"/>
-    <mergeCell ref="Z26:Z28"/>
-    <mergeCell ref="AA26:AA28"/>
-    <mergeCell ref="AB26:AB28"/>
-    <mergeCell ref="AC26:AC28"/>
-    <mergeCell ref="AD26:AD28"/>
-    <mergeCell ref="Y29:Y31"/>
-    <mergeCell ref="Z29:Z31"/>
-    <mergeCell ref="AA29:AA31"/>
-    <mergeCell ref="AB29:AB31"/>
-    <mergeCell ref="AC29:AC31"/>
-    <mergeCell ref="AD29:AD31"/>
-    <mergeCell ref="AE26:AE28"/>
-    <mergeCell ref="AE29:AE31"/>
-    <mergeCell ref="AG2:AG4"/>
-    <mergeCell ref="AG5:AG7"/>
-    <mergeCell ref="AG8:AG10"/>
-    <mergeCell ref="AG11:AG13"/>
-    <mergeCell ref="AG14:AG16"/>
-    <mergeCell ref="AG17:AG19"/>
-    <mergeCell ref="AG20:AG22"/>
-    <mergeCell ref="AG23:AG25"/>
-    <mergeCell ref="AG26:AG28"/>
-    <mergeCell ref="AG29:AG31"/>
-    <mergeCell ref="AE2:AE4"/>
-    <mergeCell ref="AE5:AE7"/>
-    <mergeCell ref="AE8:AE10"/>
-    <mergeCell ref="AE11:AE13"/>
-    <mergeCell ref="AE14:AE16"/>
-    <mergeCell ref="AE17:AE19"/>
-    <mergeCell ref="AE20:AE22"/>
-    <mergeCell ref="AE23:AE25"/>
-    <mergeCell ref="Y1:AD1"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="AH2:AH4"/>
-    <mergeCell ref="AH5:AH7"/>
-    <mergeCell ref="AH8:AH10"/>
-    <mergeCell ref="AH11:AH13"/>
-    <mergeCell ref="AH14:AH16"/>
-    <mergeCell ref="AH17:AH19"/>
-    <mergeCell ref="AH20:AH22"/>
-    <mergeCell ref="Y20:Y22"/>
-    <mergeCell ref="Z20:Z22"/>
-    <mergeCell ref="AA20:AA22"/>
-    <mergeCell ref="AB20:AB22"/>
-    <mergeCell ref="AC20:AC22"/>
-    <mergeCell ref="AD20:AD22"/>
-    <mergeCell ref="W2:W4"/>
-    <mergeCell ref="W5:W7"/>
-    <mergeCell ref="W8:W10"/>
-    <mergeCell ref="W11:W13"/>
-    <mergeCell ref="W14:W16"/>
-    <mergeCell ref="W17:W19"/>
-    <mergeCell ref="W20:W22"/>
-    <mergeCell ref="Q14:Q16"/>
-    <mergeCell ref="Q17:Q19"/>
-    <mergeCell ref="AH23:AH25"/>
-    <mergeCell ref="AH26:AH28"/>
-    <mergeCell ref="AH29:AH31"/>
-    <mergeCell ref="AJ2:AJ4"/>
-    <mergeCell ref="AJ5:AJ7"/>
-    <mergeCell ref="AJ8:AJ10"/>
-    <mergeCell ref="AJ11:AJ13"/>
-    <mergeCell ref="AJ14:AJ16"/>
-    <mergeCell ref="AJ17:AJ19"/>
-    <mergeCell ref="AJ20:AJ22"/>
-    <mergeCell ref="AJ23:AJ25"/>
-    <mergeCell ref="AJ26:AJ28"/>
-    <mergeCell ref="AJ29:AJ31"/>
-    <mergeCell ref="AK29:AK31"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AM5:AM7"/>
-    <mergeCell ref="AM8:AM10"/>
-    <mergeCell ref="AM11:AM13"/>
-    <mergeCell ref="AM14:AM16"/>
-    <mergeCell ref="AM17:AM19"/>
-    <mergeCell ref="AM20:AM22"/>
-    <mergeCell ref="AM23:AM25"/>
-    <mergeCell ref="AM26:AM28"/>
-    <mergeCell ref="AM29:AM31"/>
-    <mergeCell ref="AK2:AK4"/>
-    <mergeCell ref="AK5:AK7"/>
-    <mergeCell ref="AK8:AK10"/>
-    <mergeCell ref="AK11:AK13"/>
-    <mergeCell ref="AK14:AK16"/>
-    <mergeCell ref="AK17:AK19"/>
-    <mergeCell ref="AK20:AK22"/>
-    <mergeCell ref="AK23:AK25"/>
-    <mergeCell ref="AK26:AK28"/>
-    <mergeCell ref="AN29:AN31"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="AP5:AP7"/>
-    <mergeCell ref="AP8:AP10"/>
-    <mergeCell ref="AP11:AP13"/>
-    <mergeCell ref="AP14:AP16"/>
-    <mergeCell ref="AP17:AP19"/>
-    <mergeCell ref="AP20:AP22"/>
-    <mergeCell ref="AP23:AP25"/>
-    <mergeCell ref="AP26:AP28"/>
-    <mergeCell ref="AP29:AP31"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AN5:AN7"/>
-    <mergeCell ref="AN8:AN10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AN17:AN19"/>
-    <mergeCell ref="AN20:AN22"/>
-    <mergeCell ref="AN23:AN25"/>
-    <mergeCell ref="AN26:AN28"/>
-    <mergeCell ref="AQ29:AQ31"/>
-    <mergeCell ref="AQ2:AQ4"/>
-    <mergeCell ref="AQ5:AQ7"/>
-    <mergeCell ref="AQ8:AQ10"/>
-    <mergeCell ref="AQ11:AQ13"/>
-    <mergeCell ref="AQ14:AQ16"/>
-    <mergeCell ref="AQ17:AQ19"/>
-    <mergeCell ref="AQ20:AQ22"/>
-    <mergeCell ref="AQ23:AQ25"/>
-    <mergeCell ref="AQ26:AQ28"/>
+    <mergeCell ref="W23:W25"/>
+    <mergeCell ref="W26:W28"/>
+    <mergeCell ref="U23:U25"/>
+    <mergeCell ref="V23:V25"/>
+    <mergeCell ref="R26:R28"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="T26:T28"/>
+    <mergeCell ref="U26:U28"/>
+    <mergeCell ref="V26:V28"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="V29:V31"/>
+    <mergeCell ref="U14:U16"/>
+    <mergeCell ref="V14:V16"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="T17:T19"/>
+    <mergeCell ref="U17:U19"/>
+    <mergeCell ref="V17:V19"/>
+    <mergeCell ref="R20:R22"/>
+    <mergeCell ref="S20:S22"/>
+    <mergeCell ref="T20:T22"/>
+    <mergeCell ref="U20:U22"/>
+    <mergeCell ref="V20:V22"/>
+    <mergeCell ref="Q20:Q22"/>
+    <mergeCell ref="Q23:Q25"/>
+    <mergeCell ref="Q26:Q28"/>
+    <mergeCell ref="Q29:Q31"/>
+    <mergeCell ref="R5:R7"/>
+    <mergeCell ref="S5:S7"/>
+    <mergeCell ref="T5:T7"/>
+    <mergeCell ref="R8:R10"/>
+    <mergeCell ref="S8:S10"/>
+    <mergeCell ref="T8:T10"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="T14:T16"/>
+    <mergeCell ref="R23:R25"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="T23:T25"/>
+    <mergeCell ref="R29:R31"/>
+    <mergeCell ref="S29:S31"/>
+    <mergeCell ref="T29:T31"/>
+    <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="Q5:Q7"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="T2:T4"/>
+    <mergeCell ref="U2:U4"/>
+    <mergeCell ref="V2:V4"/>
+    <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="U5:U7"/>
+    <mergeCell ref="V5:V7"/>
+    <mergeCell ref="U8:U10"/>
+    <mergeCell ref="V8:V10"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V13"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="J23:J25"/>
+    <mergeCell ref="J26:J28"/>
+    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="I26:I28"/>
+    <mergeCell ref="I29:I31"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="K23:K25"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="K29:K31"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="L8:L10"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="L17:L19"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="K5:K7"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="K17:K19"/>
+    <mergeCell ref="L20:L22"/>
+    <mergeCell ref="L23:L25"/>
+    <mergeCell ref="L26:L28"/>
+    <mergeCell ref="L29:L31"/>
+    <mergeCell ref="O29:O31"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="N23:N25"/>
+    <mergeCell ref="N26:N28"/>
+    <mergeCell ref="N29:N31"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="O5:O7"/>
+    <mergeCell ref="O8:O10"/>
+    <mergeCell ref="O11:O13"/>
+    <mergeCell ref="O14:O16"/>
+    <mergeCell ref="O17:O19"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="N8:N10"/>
+    <mergeCell ref="N11:N13"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="N17:N19"/>
+    <mergeCell ref="O20:O22"/>
+    <mergeCell ref="O23:O25"/>
+    <mergeCell ref="O26:O28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -10995,33 +10979,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="D1" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="D1" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="20"/>
+      <c r="E1" s="21"/>
       <c r="L1" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="Q1" s="20"/>
-      <c r="S1" s="20" t="s">
+      <c r="Q1" s="21"/>
+      <c r="S1" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="20"/>
-      <c r="Y1" s="20" t="s">
+      <c r="T1" s="21"/>
+      <c r="Y1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20" t="s">
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="AB1" s="20"/>
+      <c r="AB1" s="21"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" t="s">
@@ -11673,18 +11657,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
@@ -11715,7 +11699,7 @@
       </c>
       <c r="C3">
         <f>C16</f>
-        <v>-81.344480745398442</v>
+        <v>-75.684082406722581</v>
       </c>
       <c r="D3">
         <f>E28</f>
@@ -11723,7 +11707,7 @@
       </c>
       <c r="E3" s="8">
         <f>D3/ABS(1.5*C3)</f>
-        <v>0.78184545763248758</v>
+        <v>0.84031953287728578</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G11" si="0">D16</f>
@@ -11985,9 +11969,9 @@
       <c r="D15" t="s">
         <v>107</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
     </row>
     <row r="16" spans="2:10">
       <c r="B16">
@@ -11995,7 +11979,7 @@
       </c>
       <c r="C16">
         <f>('Results_e,f'!M2*'Results_e,f'!$L2/2+'Results_e,f'!M3*'Results_e,f'!$L3/2+'Results_e,f'!O13*'Results_e,f'!$L13)/(('Results_e,f'!$L2/2)+('Results_e,f'!$L3/2)+'Results_e,f'!$L13)</f>
-        <v>-81.344480745398442</v>
+        <v>-75.684082406722581</v>
       </c>
       <c r="D16">
         <f>('Results_e,f'!N2*'Results_e,f'!$L2/2+'Results_e,f'!N3*'Results_e,f'!$L3/2+'Results_e,f'!P13*'Results_e,f'!$L13)/(('Results_e,f'!$L2/2)+('Results_e,f'!$L3/2)+'Results_e,f'!$L13)</f>
@@ -12315,55 +12299,55 @@
       <c r="C1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
     </row>
     <row r="2" spans="2:17">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="E2" s="19" t="s">
+      <c r="C2" s="23"/>
+      <c r="E2" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="L2" s="19" t="s">
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="L2" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="2:17">
       <c r="B3" cm="1">
         <f t="array" ref="B3:C32">Results_d!H2:I31</f>
-        <v>3.5083529182544098</v>
+        <v>4.915398902751015</v>
       </c>
       <c r="C3">
         <v>1.3198932375216843</v>
       </c>
       <c r="E3">
         <f>'Results_e,f'!E2</f>
-        <v>-70.752968545441874</v>
+        <v>-55.413272966050641</v>
       </c>
       <c r="F3">
         <f>'Results_e,f'!I2</f>
@@ -12379,11 +12363,11 @@
       </c>
       <c r="I3" s="13">
         <f>Results_e_continued!W2</f>
-        <v>5.3556009540869001</v>
+        <v>5.7264299320778802</v>
       </c>
       <c r="J3" cm="1">
         <f t="array" ref="J3:J12">_xlfn._xlws.FILTER(Results_e_continued!AP2:'Results_e_continued'!AP29,Results_e_continued!AQ2:'Results_e_continued'!AQ29&lt;&gt;"")</f>
-        <v>0.95474249674484579</v>
+        <v>1.2209677731796567</v>
       </c>
       <c r="L3">
         <f>'Results_e,f'!F2</f>
@@ -12919,21 +12903,21 @@
       <c r="C15">
         <v>1.3244255659481587</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
     </row>
     <row r="16" spans="2:17">
       <c r="B16">
@@ -12947,7 +12931,7 @@
       </c>
       <c r="F16">
         <f>f_RF!C3</f>
-        <v>-81.344480745398442</v>
+        <v>-75.684082406722581</v>
       </c>
       <c r="G16">
         <f>f_RF!D3</f>
@@ -12955,7 +12939,7 @@
       </c>
       <c r="H16">
         <f>f_RF!E3</f>
-        <v>0.78184545763248758</v>
+        <v>0.84031953287728578</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -13740,8 +13724,8 @@
       </c>
     </row>
     <row r="61" spans="2:3">
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Calculation.xlsx
+++ b/Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c0d169820723523/Uni/Aerospace Master/1. Semester/Aerospace Strcutures/Assignment 2/AerospaceStructures_Assignment2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{4071ACE8-B8E8-7F45-AA5C-44E61B53CA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471096F5-3BA6-4B3C-AAD3-2B1CF6E55BE5}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{4071ACE8-B8E8-7F45-AA5C-44E61B53CA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67CC735E-6B1E-4DFE-B0E4-18BC7ECD84CF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="8" xr2:uid="{774086B3-7ADF-614D-BABB-EF0864783B0B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{774086B3-7ADF-614D-BABB-EF0864783B0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Import_UngaBunga" sheetId="11" r:id="rId1"/>
@@ -3149,7 +3149,8 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-20</v>
+        <f>MIN(Import_UngaBunga!B2,Import_UngaBunga!F2)</f>
+        <v>-66.018310546875</v>
       </c>
       <c r="C2">
         <f>MIN(Import_UngaBunga!C2,Import_UngaBunga!G2)</f>
@@ -4397,7 +4398,7 @@
       </c>
       <c r="C2">
         <f>SQRT(Import!B2^2+Import!F2^2-Import!B2*Import!F2+3*Import!D2^2)</f>
-        <v>72.124359998856804</v>
+        <v>101.05026725087633</v>
       </c>
       <c r="D2">
         <f>SQRT(Import!C2^2+Import!G2^2-Import!C2*Import!G2+3*Import!E2^2)</f>
@@ -4413,7 +4414,7 @@
       </c>
       <c r="H2" s="8">
         <f>IF(C2&lt;&gt;0,$A$2/(1.5*C2),IF(E2&lt;&gt;0,$A$2/(1.5*E2),"NaN"))</f>
-        <v>4.915398902751015</v>
+        <v>3.5083529182544098</v>
       </c>
       <c r="I2" s="8">
         <f>IF(D2&lt;&gt;0,$A$2/(1.5*D2),IF(F2&lt;&gt;0,$A$2/(1.5*F2),"NaN"))</f>
@@ -6636,7 +6637,7 @@
       </c>
       <c r="E2" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B2:$B4,Import!B2:B4)/$D2</f>
-        <v>-55.413272966050641</v>
+        <v>-70.752968545441874</v>
       </c>
       <c r="F2" s="24">
         <f>SUMPRODUCT('Results_e,f'!$B2:$B4,Import!C2:C4)/$D2</f>
@@ -6667,7 +6668,7 @@
       </c>
       <c r="M2" cm="1">
         <f t="array" ref="M2:M11">_xlfn._xlws.FILTER(E2:E31,E2:E31&lt;&gt;"")</f>
-        <v>-55.413272966050641</v>
+        <v>-70.752968545441874</v>
       </c>
       <c r="N2" cm="1">
         <f t="array" ref="N2:N11">_xlfn._xlws.FILTER(F2:F31,F2:F31&lt;&gt;"")</f>
@@ -8356,7 +8357,7 @@
       </c>
       <c r="B2" s="23">
         <f>'Results_e,f'!E2</f>
-        <v>-55.413272966050641</v>
+        <v>-70.752968545441874</v>
       </c>
       <c r="C2" s="23">
         <f>'Results_e,f'!F2</f>
@@ -8380,7 +8381,7 @@
       </c>
       <c r="I2" s="23">
         <f>MAX(-MIN(B2,0),-MIN(F2,0))</f>
-        <v>55.413272966050641</v>
+        <v>70.752968545441874</v>
       </c>
       <c r="J2" s="23">
         <f>IF(-MIN(B2,0)&gt;=-MIN(F2,0),F2,B2)</f>
@@ -8396,7 +8397,7 @@
       </c>
       <c r="N2" s="23">
         <f>IF(J2&gt;0,-J2/I2,ABS(J2)/I2)</f>
-        <v>-0.43033277727355951</v>
+        <v>-0.33703388201984735</v>
       </c>
       <c r="O2" s="23">
         <f>IF(L2&gt;0,-L2/K2,ABS(L2)/K2)</f>
@@ -8404,31 +8405,31 @@
       </c>
       <c r="Q2" s="23">
         <f xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$N2*$B$40^2))</f>
-        <v>-3.8674314186628855</v>
+        <v>-5.4645571859300714</v>
       </c>
       <c r="R2" s="23">
         <f t="shared" ref="R2:V2" si="0" xml:space="preserve"> ((G$35^2+$B$40^2)^2)/($B$40^2*(G$35^2+$N2*$B$40^2))</f>
-        <v>147.85069175888054</v>
+        <v>19.424716768903426</v>
       </c>
       <c r="S2" s="23">
         <f xml:space="preserve"> ((H$35^2+$B$40^2)^2)/($B$40^2*(H$35^2+$N2*$B$40^2))</f>
-        <v>7.0216432338443271</v>
+        <v>6.0334908399040517</v>
       </c>
       <c r="T2" s="23">
         <f xml:space="preserve"> ((I$35^2+$B$40^2)^2)/($B$40^2*(I$35^2+$N2*$B$40^2))</f>
-        <v>5.7264299320778802</v>
+        <v>5.3556009540869001</v>
       </c>
       <c r="U2" s="23">
         <f xml:space="preserve"> ((J$35^2+$B$40^2)^2)/($B$40^2*(J$35^2+$N2*$B$40^2))</f>
-        <v>6.0796333610398294</v>
+        <v>5.8472357395120342</v>
       </c>
       <c r="V2" s="23">
         <f t="shared" si="0"/>
-        <v>7.0034539468655286</v>
+        <v>6.8250699555434595</v>
       </c>
       <c r="W2" s="24">
         <f>_xlfn.MINIFS(Q2:V2,Q2:V2,"&gt;0")</f>
-        <v>5.7264299320778802</v>
+        <v>5.3556009540869001</v>
       </c>
       <c r="Y2" s="23">
         <f xml:space="preserve"> ((F$35^2+$B$40^2)^2)/($B$40^2*(F$35^2+$O2*$B$40^2))</f>
@@ -8460,7 +8461,7 @@
       </c>
       <c r="AG2" s="23">
         <f>W2*$B$41</f>
-        <v>132.92773182300081</v>
+        <v>124.31967138687214</v>
       </c>
       <c r="AH2" s="23">
         <f>AE2*$B$41</f>
@@ -8468,7 +8469,7 @@
       </c>
       <c r="AJ2" s="23">
         <f>1.5*I2 / AG2</f>
-        <v>0.62530149509926058</v>
+        <v>0.85368189630985314</v>
       </c>
       <c r="AK2" s="23">
         <f>1.5*K2 / AH2</f>
@@ -8484,7 +8485,7 @@
       </c>
       <c r="AP2" s="24">
         <f>1/((AJ2)+(AM2)^2)</f>
-        <v>1.2209677731796567</v>
+        <v>0.95474249674484579</v>
       </c>
       <c r="AQ2" s="24">
         <f>1/((AK2)+(AN2)^2)</f>
@@ -11699,7 +11700,7 @@
       </c>
       <c r="C3">
         <f>C16</f>
-        <v>-75.684082406722581</v>
+        <v>-81.344480745398442</v>
       </c>
       <c r="D3">
         <f>E28</f>
@@ -11707,7 +11708,7 @@
       </c>
       <c r="E3" s="8">
         <f>D3/ABS(1.5*C3)</f>
-        <v>0.84031953287728578</v>
+        <v>0.78184545763248758</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G11" si="0">D16</f>
@@ -11979,7 +11980,7 @@
       </c>
       <c r="C16">
         <f>('Results_e,f'!M2*'Results_e,f'!$L2/2+'Results_e,f'!M3*'Results_e,f'!$L3/2+'Results_e,f'!O13*'Results_e,f'!$L13)/(('Results_e,f'!$L2/2)+('Results_e,f'!$L3/2)+'Results_e,f'!$L13)</f>
-        <v>-75.684082406722581</v>
+        <v>-81.344480745398442</v>
       </c>
       <c r="D16">
         <f>('Results_e,f'!N2*'Results_e,f'!$L2/2+'Results_e,f'!N3*'Results_e,f'!$L3/2+'Results_e,f'!P13*'Results_e,f'!$L13)/(('Results_e,f'!$L2/2)+('Results_e,f'!$L3/2)+'Results_e,f'!$L13)</f>
@@ -12340,14 +12341,14 @@
     <row r="3" spans="2:17">
       <c r="B3" cm="1">
         <f t="array" ref="B3:C32">Results_d!H2:I31</f>
-        <v>4.915398902751015</v>
+        <v>3.5083529182544098</v>
       </c>
       <c r="C3">
         <v>1.3198932375216843</v>
       </c>
       <c r="E3">
         <f>'Results_e,f'!E2</f>
-        <v>-55.413272966050641</v>
+        <v>-70.752968545441874</v>
       </c>
       <c r="F3">
         <f>'Results_e,f'!I2</f>
@@ -12363,11 +12364,11 @@
       </c>
       <c r="I3" s="13">
         <f>Results_e_continued!W2</f>
-        <v>5.7264299320778802</v>
+        <v>5.3556009540869001</v>
       </c>
       <c r="J3" cm="1">
         <f t="array" ref="J3:J12">_xlfn._xlws.FILTER(Results_e_continued!AP2:'Results_e_continued'!AP29,Results_e_continued!AQ2:'Results_e_continued'!AQ29&lt;&gt;"")</f>
-        <v>1.2209677731796567</v>
+        <v>0.95474249674484579</v>
       </c>
       <c r="L3">
         <f>'Results_e,f'!F2</f>
@@ -12931,7 +12932,7 @@
       </c>
       <c r="F16">
         <f>f_RF!C3</f>
-        <v>-75.684082406722581</v>
+        <v>-81.344480745398442</v>
       </c>
       <c r="G16">
         <f>f_RF!D3</f>
@@ -12939,7 +12940,7 @@
       </c>
       <c r="H16">
         <f>f_RF!E3</f>
-        <v>0.84031953287728578</v>
+        <v>0.78184545763248758</v>
       </c>
       <c r="K16">
         <v>1</v>
